--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R11" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R12" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671155</v>
+        <v>127670217</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449421</v>
+        <v>449200</v>
       </c>
       <c r="R28" t="n">
-        <v>6720319</v>
+        <v>6720125</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R29" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670762</v>
+        <v>127671155</v>
       </c>
       <c r="B30" t="n">
         <v>79018</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449570</v>
+        <v>449421</v>
       </c>
       <c r="R30" t="n">
-        <v>6720155</v>
+        <v>6720319</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670217</v>
+        <v>127671028</v>
       </c>
       <c r="B31" t="n">
         <v>79018</v>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449200</v>
+        <v>449628</v>
       </c>
       <c r="R31" t="n">
-        <v>6720125</v>
+        <v>6720374</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3733,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127669984</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,21 +3744,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449175</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720229</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670445</v>
+        <v>127670934</v>
       </c>
       <c r="B34" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449296</v>
+        <v>449622</v>
       </c>
       <c r="R34" t="n">
-        <v>6720275</v>
+        <v>6720346</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B36" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R36" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127671216</v>
+        <v>127670445</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449453</v>
+        <v>449296</v>
       </c>
       <c r="R37" t="n">
-        <v>6720203</v>
+        <v>6720275</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671241</v>
+        <v>127670625</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449445</v>
+        <v>449440</v>
       </c>
       <c r="R44" t="n">
-        <v>6720188</v>
+        <v>6720118</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670625</v>
+        <v>127670593</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449440</v>
+        <v>449457</v>
       </c>
       <c r="R45" t="n">
-        <v>6720118</v>
+        <v>6720089</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670593</v>
+        <v>127671241</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449457</v>
+        <v>449445</v>
       </c>
       <c r="R46" t="n">
-        <v>6720089</v>
+        <v>6720188</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670889</v>
+        <v>127670168</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449605</v>
+        <v>449195</v>
       </c>
       <c r="R48" t="n">
-        <v>6720315</v>
+        <v>6720146</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670722</v>
+        <v>127670889</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5470,21 +5470,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449567</v>
+        <v>449605</v>
       </c>
       <c r="R49" t="n">
-        <v>6720141</v>
+        <v>6720315</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670168</v>
+        <v>127670722</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449195</v>
+        <v>449567</v>
       </c>
       <c r="R50" t="n">
-        <v>6720146</v>
+        <v>6720141</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670710</v>
+        <v>127670054</v>
       </c>
       <c r="B74" t="n">
-        <v>78777</v>
+        <v>91350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,24 +8008,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8035,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449560</v>
+        <v>449185</v>
       </c>
       <c r="R74" t="n">
-        <v>6720133</v>
+        <v>6720192</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8199,10 +8203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670054</v>
+        <v>127670710</v>
       </c>
       <c r="B76" t="n">
-        <v>91350</v>
+        <v>78777</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8210,28 +8214,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449185</v>
+        <v>449560</v>
       </c>
       <c r="R76" t="n">
-        <v>6720192</v>
+        <v>6720133</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127670008</v>
+        <v>127671164</v>
       </c>
       <c r="B2" t="n">
         <v>79018</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449167</v>
+        <v>449428</v>
       </c>
       <c r="R2" t="n">
-        <v>6720240</v>
+        <v>6720312</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127671164</v>
+        <v>127670008</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449428</v>
+        <v>449167</v>
       </c>
       <c r="R3" t="n">
-        <v>6720312</v>
+        <v>6720240</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,43 +877,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127670907</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449605</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720348</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -984,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127670574</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,26 +993,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449419</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720156</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1066,7 +1069,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670618</v>
+        <v>127670874</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449457</v>
+        <v>449564</v>
       </c>
       <c r="R7" t="n">
-        <v>6720117</v>
+        <v>6720313</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670574</v>
+        <v>127671038</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,31 +1300,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1330,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449419</v>
+        <v>449628</v>
       </c>
       <c r="R8" t="n">
-        <v>6720156</v>
+        <v>6720382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1374,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670907</v>
+        <v>127670618</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,28 +1401,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1434,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449605</v>
+        <v>449457</v>
       </c>
       <c r="R9" t="n">
-        <v>6720348</v>
+        <v>6720117</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1497,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670874</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449564</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720313</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R11" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R12" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R16" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2182,6 +2182,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2321,21 +2326,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R18" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2384,11 +2389,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,42 +2517,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670094</v>
+        <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449196</v>
+        <v>449363</v>
       </c>
       <c r="R20" t="n">
-        <v>6720173</v>
+        <v>6720137</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2604,6 +2599,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2622,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670476</v>
+        <v>127670000</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449363</v>
+        <v>449159</v>
       </c>
       <c r="R21" t="n">
-        <v>6720137</v>
+        <v>6720222</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2723,37 +2719,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670496</v>
+        <v>127670094</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449359</v>
+        <v>449196</v>
       </c>
       <c r="R22" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2805,7 +2806,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670000</v>
+        <v>127670496</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449159</v>
+        <v>449359</v>
       </c>
       <c r="R23" t="n">
-        <v>6720222</v>
+        <v>6720133</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670118</v>
+        <v>127670032</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449175</v>
+        <v>449165</v>
       </c>
       <c r="R24" t="n">
-        <v>6720175</v>
+        <v>6720228</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670032</v>
+        <v>127670849</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449165</v>
+        <v>449556</v>
       </c>
       <c r="R25" t="n">
-        <v>6720228</v>
+        <v>6720283</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670849</v>
+        <v>127670299</v>
       </c>
       <c r="B26" t="n">
         <v>79018</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449556</v>
+        <v>449181</v>
       </c>
       <c r="R26" t="n">
-        <v>6720283</v>
+        <v>6720023</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670299</v>
+        <v>127670118</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449181</v>
+        <v>449175</v>
       </c>
       <c r="R27" t="n">
-        <v>6720023</v>
+        <v>6720175</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127670217</v>
+        <v>127671155</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449200</v>
+        <v>449421</v>
       </c>
       <c r="R28" t="n">
-        <v>6720125</v>
+        <v>6720319</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127669984</v>
+        <v>127670556</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449175</v>
+        <v>449417</v>
       </c>
       <c r="R29" t="n">
-        <v>6720229</v>
+        <v>6720161</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3504,6 +3504,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,7 +3536,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127671155</v>
+        <v>127670217</v>
       </c>
       <c r="B30" t="n">
         <v>79018</v>
@@ -3569,10 +3574,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449421</v>
+        <v>449200</v>
       </c>
       <c r="R30" t="n">
-        <v>6720319</v>
+        <v>6720125</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3632,7 +3637,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127671028</v>
+        <v>127670762</v>
       </c>
       <c r="B31" t="n">
         <v>79018</v>
@@ -3670,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449628</v>
+        <v>449570</v>
       </c>
       <c r="R31" t="n">
-        <v>6720374</v>
+        <v>6720155</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3733,7 +3738,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127671028</v>
       </c>
       <c r="B32" t="n">
         <v>79018</v>
@@ -3771,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449628</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720374</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3834,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670556</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3845,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3872,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449417</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720161</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3908,11 +3913,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B35" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R35" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127670448</v>
+        <v>127671241</v>
       </c>
       <c r="B41" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4662,21 +4662,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449292</v>
+        <v>449445</v>
       </c>
       <c r="R41" t="n">
-        <v>6720271</v>
+        <v>6720188</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,7 +4752,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670364</v>
+        <v>127670625</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449245</v>
+        <v>449440</v>
       </c>
       <c r="R42" t="n">
-        <v>6720058</v>
+        <v>6720118</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670309</v>
+        <v>127670364</v>
       </c>
       <c r="B43" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449202</v>
+        <v>449245</v>
       </c>
       <c r="R43" t="n">
-        <v>6720026</v>
+        <v>6720058</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670625</v>
+        <v>127670593</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449440</v>
+        <v>449457</v>
       </c>
       <c r="R44" t="n">
-        <v>6720118</v>
+        <v>6720089</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670593</v>
+        <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449457</v>
+        <v>449202</v>
       </c>
       <c r="R45" t="n">
-        <v>6720089</v>
+        <v>6720026</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671241</v>
+        <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5167,21 +5167,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449445</v>
+        <v>449292</v>
       </c>
       <c r="R46" t="n">
-        <v>6720188</v>
+        <v>6720271</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670168</v>
+        <v>127670889</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449195</v>
+        <v>449605</v>
       </c>
       <c r="R48" t="n">
-        <v>6720146</v>
+        <v>6720315</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670889</v>
+        <v>127670168</v>
       </c>
       <c r="B49" t="n">
         <v>79018</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449605</v>
+        <v>449195</v>
       </c>
       <c r="R49" t="n">
-        <v>6720315</v>
+        <v>6720146</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5661,46 +5661,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669856</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>56853</v>
+        <v>91330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5708,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449125</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720233</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5752,6 +5743,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5770,7 +5762,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670921</v>
+        <v>127670754</v>
       </c>
       <c r="B52" t="n">
         <v>79018</v>
@@ -5808,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449580</v>
+        <v>449589</v>
       </c>
       <c r="R52" t="n">
-        <v>6720362</v>
+        <v>6720140</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5871,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670649</v>
+        <v>127670788</v>
       </c>
       <c r="B53" t="n">
         <v>79018</v>
@@ -5909,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449438</v>
+        <v>449583</v>
       </c>
       <c r="R53" t="n">
-        <v>6720136</v>
+        <v>6720169</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670788</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6010,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449583</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720169</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6111,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670754</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
         <v>79018</v>
@@ -6212,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449589</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720140</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,10 +6267,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671194</v>
+        <v>127670921</v>
       </c>
       <c r="B57" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6286,21 +6278,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6313,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449456</v>
+        <v>449580</v>
       </c>
       <c r="R57" t="n">
-        <v>6720223</v>
+        <v>6720362</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671143</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449435</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720323</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671129</v>
+        <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449427</v>
+        <v>449202</v>
       </c>
       <c r="R59" t="n">
-        <v>6720322</v>
+        <v>6720148</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670181</v>
+        <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449202</v>
+        <v>449576</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720141</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670743</v>
+        <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449576</v>
+        <v>449427</v>
       </c>
       <c r="R62" t="n">
-        <v>6720141</v>
+        <v>6720322</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127669907</v>
+        <v>127670953</v>
       </c>
       <c r="B66" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449153</v>
+        <v>449638</v>
       </c>
       <c r="R66" t="n">
-        <v>6720237</v>
+        <v>6720356</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670953</v>
+        <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449638</v>
+        <v>449153</v>
       </c>
       <c r="R69" t="n">
-        <v>6720356</v>
+        <v>6720237</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670825</v>
+        <v>127670324</v>
       </c>
       <c r="B70" t="n">
         <v>79018</v>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449573</v>
+        <v>449217</v>
       </c>
       <c r="R70" t="n">
-        <v>6720260</v>
+        <v>6720024</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670200</v>
+        <v>127670825</v>
       </c>
       <c r="B71" t="n">
         <v>79018</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449202</v>
+        <v>449573</v>
       </c>
       <c r="R71" t="n">
-        <v>6720096</v>
+        <v>6720260</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670485</v>
+        <v>127670200</v>
       </c>
       <c r="B72" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449358</v>
+        <v>449202</v>
       </c>
       <c r="R72" t="n">
-        <v>6720139</v>
+        <v>6720096</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670324</v>
+        <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449217</v>
+        <v>449358</v>
       </c>
       <c r="R73" t="n">
-        <v>6720024</v>
+        <v>6720139</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670272</v>
+        <v>127671250</v>
       </c>
       <c r="B75" t="n">
         <v>79018</v>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449168</v>
+        <v>449429</v>
       </c>
       <c r="R75" t="n">
-        <v>6720012</v>
+        <v>6720186</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670710</v>
+        <v>127670272</v>
       </c>
       <c r="B76" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449560</v>
+        <v>449168</v>
       </c>
       <c r="R76" t="n">
-        <v>6720133</v>
+        <v>6720012</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127671250</v>
+        <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449429</v>
+        <v>449560</v>
       </c>
       <c r="R77" t="n">
-        <v>6720186</v>
+        <v>6720133</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,41 +877,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670907</v>
+        <v>127671018</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449605</v>
+        <v>449633</v>
       </c>
       <c r="R4" t="n">
-        <v>6720348</v>
+        <v>6720378</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670574</v>
+        <v>127670907</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,31 +995,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1025,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449419</v>
+        <v>449605</v>
       </c>
       <c r="R5" t="n">
-        <v>6720156</v>
+        <v>6720348</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1069,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1491,41 +1493,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,42 +2002,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127671090</v>
+        <v>127670513</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449480</v>
+        <v>449366</v>
       </c>
       <c r="R15" t="n">
-        <v>6720296</v>
+        <v>6720133</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2081,6 +2076,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670513</v>
+        <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449366</v>
+        <v>449579</v>
       </c>
       <c r="R16" t="n">
-        <v>6720133</v>
+        <v>6720260</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2182,11 +2182,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670838</v>
+        <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449579</v>
+        <v>449454</v>
       </c>
       <c r="R17" t="n">
-        <v>6720260</v>
+        <v>6720176</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127671236</v>
+        <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>98368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449454</v>
+        <v>449480</v>
       </c>
       <c r="R18" t="n">
-        <v>6720176</v>
+        <v>6720296</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,37 +2416,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670771</v>
+        <v>127670094</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449600</v>
+        <v>449196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720158</v>
+        <v>6720173</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2498,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2517,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670476</v>
+        <v>127670496</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449363</v>
+        <v>449359</v>
       </c>
       <c r="R20" t="n">
-        <v>6720137</v>
+        <v>6720133</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2618,7 +2622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670000</v>
+        <v>127670771</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2656,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449159</v>
+        <v>449600</v>
       </c>
       <c r="R21" t="n">
-        <v>6720222</v>
+        <v>6720158</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2719,42 +2723,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670094</v>
+        <v>127670476</v>
       </c>
       <c r="B22" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2762,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449196</v>
+        <v>449363</v>
       </c>
       <c r="R22" t="n">
-        <v>6720173</v>
+        <v>6720137</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2806,6 +2805,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670496</v>
+        <v>127670000</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449359</v>
+        <v>449159</v>
       </c>
       <c r="R23" t="n">
-        <v>6720133</v>
+        <v>6720222</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -4445,39 +4445,35 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127670266</v>
+        <v>127670702</v>
       </c>
       <c r="B39" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4487,10 +4483,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449176</v>
+        <v>449550</v>
       </c>
       <c r="R39" t="n">
-        <v>6720025</v>
+        <v>6720131</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4550,35 +4546,39 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127670702</v>
+        <v>127670266</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449550</v>
+        <v>449176</v>
       </c>
       <c r="R40" t="n">
-        <v>6720131</v>
+        <v>6720025</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127670754</v>
       </c>
       <c r="B51" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449589</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720140</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,7 +5762,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670754</v>
+        <v>127670788</v>
       </c>
       <c r="B52" t="n">
         <v>79018</v>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449589</v>
+        <v>449583</v>
       </c>
       <c r="R52" t="n">
-        <v>6720140</v>
+        <v>6720169</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670788</v>
+        <v>127671143</v>
       </c>
       <c r="B53" t="n">
         <v>79018</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449583</v>
+        <v>449435</v>
       </c>
       <c r="R53" t="n">
-        <v>6720169</v>
+        <v>6720323</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670649</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449438</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720136</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670649</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449438</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720136</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670921</v>
       </c>
       <c r="B56" t="n">
         <v>79018</v>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449580</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720362</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,37 +6267,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670921</v>
+        <v>127669856</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6305,10 +6314,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449580</v>
+        <v>449125</v>
       </c>
       <c r="R57" t="n">
-        <v>6720362</v>
+        <v>6720233</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6349,7 +6358,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127671194</v>
       </c>
       <c r="B58" t="n">
-        <v>56853</v>
+        <v>91330</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449456</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720223</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127671164</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127670008</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127671175</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449421</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720306</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -984,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670907</v>
+        <v>127670874</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>78778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,28 +989,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1026,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449605</v>
+        <v>449564</v>
       </c>
       <c r="R5" t="n">
-        <v>6720348</v>
+        <v>6720313</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1089,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671175</v>
+        <v>127671038</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R6" t="n">
-        <v>6720306</v>
+        <v>6720382</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670874</v>
+        <v>127670618</v>
       </c>
       <c r="B7" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449564</v>
+        <v>449457</v>
       </c>
       <c r="R7" t="n">
-        <v>6720313</v>
+        <v>6720117</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1291,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127671038</v>
+        <v>127670907</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,24 +1292,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1329,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R8" t="n">
-        <v>6720382</v>
+        <v>6720348</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1392,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670618</v>
+        <v>127670574</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,26 +1397,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449457</v>
+        <v>449419</v>
       </c>
       <c r="R9" t="n">
-        <v>6720117</v>
+        <v>6720156</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1474,7 +1473,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,40 +1491,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R11" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B12" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R12" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1803,7 +1803,7 @@
         <v>127670132</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>127671204</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>127670513</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,42 +2416,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670094</v>
+        <v>127670771</v>
       </c>
       <c r="B19" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449196</v>
+        <v>449600</v>
       </c>
       <c r="R19" t="n">
-        <v>6720173</v>
+        <v>6720158</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,6 +2498,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670496</v>
+        <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449359</v>
+        <v>449363</v>
       </c>
       <c r="R20" t="n">
-        <v>6720133</v>
+        <v>6720137</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2622,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670771</v>
+        <v>127670000</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2660,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449600</v>
+        <v>449159</v>
       </c>
       <c r="R21" t="n">
-        <v>6720158</v>
+        <v>6720222</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2723,37 +2719,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670476</v>
+        <v>127670094</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449363</v>
+        <v>449196</v>
       </c>
       <c r="R22" t="n">
-        <v>6720137</v>
+        <v>6720173</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2805,7 +2806,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670000</v>
+        <v>127670496</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449159</v>
+        <v>449359</v>
       </c>
       <c r="R23" t="n">
-        <v>6720222</v>
+        <v>6720133</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2928,7 +2928,7 @@
         <v>127670032</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>127670849</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>127670299</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>127670118</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>127671155</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>127670556</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>127670217</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127670762</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>127671028</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>127671216</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127670934</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>127670445</v>
       </c>
       <c r="B37" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>127670341</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127670702</v>
       </c>
       <c r="B39" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>127670266</v>
       </c>
       <c r="B40" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>127671241</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>127670625</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>127670364</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>127670593</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>127670889</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>127670168</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>127670722</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670754</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449589</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720140</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670788</v>
+        <v>127670754</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449583</v>
+        <v>449589</v>
       </c>
       <c r="R52" t="n">
-        <v>6720169</v>
+        <v>6720140</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671143</v>
+        <v>127670788</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449435</v>
+        <v>449583</v>
       </c>
       <c r="R53" t="n">
-        <v>6720323</v>
+        <v>6720169</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,10 +5964,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670921</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449580</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720362</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,46 +6267,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669856</v>
+        <v>127670921</v>
       </c>
       <c r="B57" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6314,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449125</v>
+        <v>449580</v>
       </c>
       <c r="R57" t="n">
-        <v>6720233</v>
+        <v>6720362</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6358,6 +6349,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>91330</v>
+        <v>56855</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>127670781</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>127670953</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>127670541</v>
       </c>
       <c r="B67" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>127670605</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>127670324</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>127670825</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>127670200</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670054</v>
+        <v>127671250</v>
       </c>
       <c r="B74" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,28 +8008,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8039,10 +8035,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449185</v>
+        <v>449429</v>
       </c>
       <c r="R74" t="n">
-        <v>6720192</v>
+        <v>6720186</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8102,10 +8098,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127671250</v>
+        <v>127670272</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8140,10 +8136,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449429</v>
+        <v>449168</v>
       </c>
       <c r="R75" t="n">
-        <v>6720186</v>
+        <v>6720012</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8203,10 +8199,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670272</v>
+        <v>127670054</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8214,24 +8210,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449168</v>
+        <v>449185</v>
       </c>
       <c r="R76" t="n">
-        <v>6720012</v>
+        <v>6720192</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8307,7 +8307,7 @@
         <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1386,40 +1386,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R9" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1473,6 +1474,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,41 +1493,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R11" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R12" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671155</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449421</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720319</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127670556</v>
+        <v>127671155</v>
       </c>
       <c r="B29" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449417</v>
+        <v>449421</v>
       </c>
       <c r="R29" t="n">
-        <v>6720161</v>
+        <v>6720319</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3504,11 +3504,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3536,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670217</v>
+        <v>127670556</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3542,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449200</v>
+        <v>449417</v>
       </c>
       <c r="R30" t="n">
-        <v>6720125</v>
+        <v>6720161</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3610,6 +3605,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,7 +3637,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670762</v>
+        <v>127670217</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449570</v>
+        <v>449200</v>
       </c>
       <c r="R31" t="n">
-        <v>6720155</v>
+        <v>6720125</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127671028</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449628</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720374</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B33" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R35" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127670445</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449296</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720275</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670445</v>
+        <v>127671229</v>
       </c>
       <c r="B37" t="n">
-        <v>78779</v>
+        <v>91332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449296</v>
+        <v>449442</v>
       </c>
       <c r="R37" t="n">
-        <v>6720275</v>
+        <v>6720178</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670953</v>
+        <v>127669907</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449638</v>
+        <v>449153</v>
       </c>
       <c r="R66" t="n">
-        <v>6720356</v>
+        <v>6720237</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B67" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R67" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,11 +7359,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7391,10 +7386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7402,21 +7397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7429,10 +7424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R68" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7465,6 +7460,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127669907</v>
+        <v>127670605</v>
       </c>
       <c r="B69" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449153</v>
+        <v>449451</v>
       </c>
       <c r="R69" t="n">
-        <v>6720237</v>
+        <v>6720105</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671250</v>
+        <v>127670710</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,21 +8008,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449429</v>
+        <v>449560</v>
       </c>
       <c r="R74" t="n">
-        <v>6720186</v>
+        <v>6720133</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670272</v>
+        <v>127671250</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449168</v>
+        <v>449429</v>
       </c>
       <c r="R75" t="n">
-        <v>6720012</v>
+        <v>6720186</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8199,10 +8199,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670054</v>
+        <v>127670272</v>
       </c>
       <c r="B76" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8210,28 +8210,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -8241,10 +8237,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449185</v>
+        <v>449168</v>
       </c>
       <c r="R76" t="n">
-        <v>6720192</v>
+        <v>6720012</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8304,10 +8300,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670710</v>
+        <v>127670054</v>
       </c>
       <c r="B77" t="n">
-        <v>78779</v>
+        <v>91352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,24 +8311,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449560</v>
+        <v>449185</v>
       </c>
       <c r="R77" t="n">
-        <v>6720133</v>
+        <v>6720192</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671216</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449453</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720203</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671216</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449453</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720203</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670445</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449296</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720275</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127671229</v>
+        <v>127670445</v>
       </c>
       <c r="B37" t="n">
-        <v>91332</v>
+        <v>78779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449442</v>
+        <v>449296</v>
       </c>
       <c r="R37" t="n">
-        <v>6720178</v>
+        <v>6720275</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670152</v>
+        <v>127670731</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449210</v>
+        <v>449569</v>
       </c>
       <c r="R63" t="n">
-        <v>6720149</v>
+        <v>6720138</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670981</v>
+        <v>127670152</v>
       </c>
       <c r="B64" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7020,10 +7020,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449656</v>
+        <v>449210</v>
       </c>
       <c r="R64" t="n">
-        <v>6720358</v>
+        <v>6720149</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127670731</v>
+        <v>127670981</v>
       </c>
       <c r="B65" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,21 +7094,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449569</v>
+        <v>449656</v>
       </c>
       <c r="R65" t="n">
-        <v>6720138</v>
+        <v>6720358</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670874</v>
+        <v>127671038</v>
       </c>
       <c r="B5" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449564</v>
+        <v>449628</v>
       </c>
       <c r="R5" t="n">
-        <v>6720313</v>
+        <v>6720382</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671038</v>
+        <v>127670618</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449628</v>
+        <v>449457</v>
       </c>
       <c r="R6" t="n">
-        <v>6720382</v>
+        <v>6720117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670618</v>
+        <v>127670907</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,24 +1191,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1218,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449457</v>
+        <v>449605</v>
       </c>
       <c r="R7" t="n">
-        <v>6720117</v>
+        <v>6720348</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1281,41 +1285,43 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670907</v>
+        <v>127671018</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1323,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449605</v>
+        <v>449633</v>
       </c>
       <c r="R8" t="n">
-        <v>6720348</v>
+        <v>6720378</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1386,41 +1392,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1430,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R9" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1474,7 +1479,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1493,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127670874</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>78778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,31 +1508,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449564</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720313</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R15" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2076,11 +2076,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670838</v>
+        <v>127670513</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449579</v>
+        <v>449366</v>
       </c>
       <c r="R16" t="n">
-        <v>6720260</v>
+        <v>6720133</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2182,6 +2177,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127671236</v>
+        <v>127670838</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449454</v>
+        <v>449579</v>
       </c>
       <c r="R17" t="n">
-        <v>6720176</v>
+        <v>6720260</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670476</v>
+        <v>127670000</v>
       </c>
       <c r="B20" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449363</v>
+        <v>449159</v>
       </c>
       <c r="R20" t="n">
-        <v>6720137</v>
+        <v>6720222</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670000</v>
+        <v>127670476</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449159</v>
+        <v>449363</v>
       </c>
       <c r="R21" t="n">
-        <v>6720222</v>
+        <v>6720137</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670032</v>
+        <v>127670849</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449165</v>
+        <v>449556</v>
       </c>
       <c r="R24" t="n">
-        <v>6720228</v>
+        <v>6720283</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670849</v>
+        <v>127670299</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449556</v>
+        <v>449181</v>
       </c>
       <c r="R25" t="n">
-        <v>6720283</v>
+        <v>6720023</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670299</v>
+        <v>127670032</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449181</v>
+        <v>449165</v>
       </c>
       <c r="R26" t="n">
-        <v>6720023</v>
+        <v>6720228</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127670556</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449417</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720161</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3403,6 +3403,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3531,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670556</v>
+        <v>127670217</v>
       </c>
       <c r="B30" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3542,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3569,10 +3574,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449417</v>
+        <v>449200</v>
       </c>
       <c r="R30" t="n">
-        <v>6720161</v>
+        <v>6720125</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3605,11 +3610,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,7 +3637,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670217</v>
+        <v>127670762</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449200</v>
+        <v>449570</v>
       </c>
       <c r="R31" t="n">
-        <v>6720125</v>
+        <v>6720155</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127671028</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449628</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720374</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127670934</v>
       </c>
       <c r="B34" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449622</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720346</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671216</v>
+        <v>127671229</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449453</v>
+        <v>449442</v>
       </c>
       <c r="R35" t="n">
-        <v>6720203</v>
+        <v>6720178</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127671216</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449453</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720203</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671241</v>
+        <v>127670625</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449445</v>
+        <v>449440</v>
       </c>
       <c r="R41" t="n">
-        <v>6720188</v>
+        <v>6720118</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670625</v>
+        <v>127670448</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449440</v>
+        <v>449292</v>
       </c>
       <c r="R42" t="n">
-        <v>6720118</v>
+        <v>6720271</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670364</v>
+        <v>127671241</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449245</v>
+        <v>449445</v>
       </c>
       <c r="R43" t="n">
-        <v>6720058</v>
+        <v>6720188</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670593</v>
+        <v>127670364</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449457</v>
+        <v>449245</v>
       </c>
       <c r="R44" t="n">
-        <v>6720089</v>
+        <v>6720058</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670309</v>
+        <v>127670593</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449202</v>
+        <v>449457</v>
       </c>
       <c r="R45" t="n">
-        <v>6720026</v>
+        <v>6720089</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670448</v>
+        <v>127670309</v>
       </c>
       <c r="B46" t="n">
         <v>78779</v>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449292</v>
+        <v>449202</v>
       </c>
       <c r="R46" t="n">
-        <v>6720271</v>
+        <v>6720026</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670889</v>
+        <v>127670722</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449605</v>
+        <v>449567</v>
       </c>
       <c r="R48" t="n">
-        <v>6720315</v>
+        <v>6720141</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670168</v>
+        <v>127670889</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449195</v>
+        <v>449605</v>
       </c>
       <c r="R49" t="n">
-        <v>6720146</v>
+        <v>6720315</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670722</v>
+        <v>127670168</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449567</v>
+        <v>449195</v>
       </c>
       <c r="R50" t="n">
-        <v>6720141</v>
+        <v>6720146</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,37 +5661,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B51" t="n">
-        <v>91332</v>
+        <v>56855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5699,10 +5708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5743,7 +5752,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670754</v>
+        <v>127671194</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5808,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449589</v>
+        <v>449456</v>
       </c>
       <c r="R52" t="n">
-        <v>6720140</v>
+        <v>6720223</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5871,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670788</v>
+        <v>127670754</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -5901,10 +5909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449583</v>
+        <v>449589</v>
       </c>
       <c r="R53" t="n">
-        <v>6720169</v>
+        <v>6720140</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670788</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -6002,10 +6010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449583</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720169</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6073,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B55" t="n">
         <v>79020</v>
@@ -6103,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R55" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6174,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B56" t="n">
         <v>79020</v>
@@ -6204,10 +6212,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,7 +6275,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670921</v>
+        <v>127670280</v>
       </c>
       <c r="B57" t="n">
         <v>79020</v>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449580</v>
+        <v>449176</v>
       </c>
       <c r="R57" t="n">
-        <v>6720362</v>
+        <v>6720013</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127670921</v>
       </c>
       <c r="B58" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449580</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720362</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670743</v>
+        <v>127670781</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449576</v>
+        <v>449586</v>
       </c>
       <c r="R60" t="n">
-        <v>6720141</v>
+        <v>6720154</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670781</v>
+        <v>127670743</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449586</v>
+        <v>449576</v>
       </c>
       <c r="R61" t="n">
-        <v>6720154</v>
+        <v>6720141</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670731</v>
+        <v>127670981</v>
       </c>
       <c r="B63" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449569</v>
+        <v>449656</v>
       </c>
       <c r="R63" t="n">
-        <v>6720138</v>
+        <v>6720358</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127670981</v>
+        <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,21 +7094,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449656</v>
+        <v>449569</v>
       </c>
       <c r="R65" t="n">
-        <v>6720358</v>
+        <v>6720138</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127669907</v>
+        <v>127670541</v>
       </c>
       <c r="B66" t="n">
-        <v>78779</v>
+        <v>80123</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449153</v>
+        <v>449410</v>
       </c>
       <c r="R66" t="n">
-        <v>6720237</v>
+        <v>6720148</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7258,6 +7258,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7285,10 +7290,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670953</v>
+        <v>127669907</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7301,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7328,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449638</v>
+        <v>449153</v>
       </c>
       <c r="R67" t="n">
-        <v>6720356</v>
+        <v>6720237</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7386,10 +7391,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B68" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7397,21 +7402,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7424,10 +7429,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R68" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7460,11 +7465,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670324</v>
+        <v>127670485</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7604,21 +7604,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449217</v>
+        <v>449358</v>
       </c>
       <c r="R70" t="n">
-        <v>6720024</v>
+        <v>6720139</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670825</v>
+        <v>127670324</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449573</v>
+        <v>449217</v>
       </c>
       <c r="R71" t="n">
-        <v>6720260</v>
+        <v>6720024</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670200</v>
+        <v>127670825</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449202</v>
+        <v>449573</v>
       </c>
       <c r="R72" t="n">
-        <v>6720096</v>
+        <v>6720260</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670485</v>
+        <v>127670200</v>
       </c>
       <c r="B73" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449358</v>
+        <v>449202</v>
       </c>
       <c r="R73" t="n">
-        <v>6720139</v>
+        <v>6720096</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,37 +877,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671175</v>
+        <v>127671018</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449421</v>
+        <v>449633</v>
       </c>
       <c r="R4" t="n">
-        <v>6720306</v>
+        <v>6720378</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127670907</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>91358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,24 +995,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1016,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720348</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670618</v>
+        <v>127671175</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1117,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449457</v>
+        <v>449421</v>
       </c>
       <c r="R6" t="n">
-        <v>6720117</v>
+        <v>6720306</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670907</v>
+        <v>127670874</v>
       </c>
       <c r="B7" t="n">
-        <v>91352</v>
+        <v>78778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,28 +1201,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1222,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449605</v>
+        <v>449564</v>
       </c>
       <c r="R7" t="n">
-        <v>6720348</v>
+        <v>6720313</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1285,43 +1291,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127671018</v>
+        <v>127671038</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449633</v>
+        <v>449628</v>
       </c>
       <c r="R8" t="n">
-        <v>6720378</v>
+        <v>6720382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670574</v>
+        <v>127670618</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,31 +1403,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1435,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449419</v>
+        <v>449457</v>
       </c>
       <c r="R9" t="n">
-        <v>6720156</v>
+        <v>6720117</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1479,6 +1474,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1497,10 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670874</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>78778</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,26 +1504,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449564</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720313</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R15" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2076,6 +2076,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670513</v>
+        <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449366</v>
+        <v>449579</v>
       </c>
       <c r="R16" t="n">
-        <v>6720133</v>
+        <v>6720260</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2177,11 +2182,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670838</v>
+        <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449579</v>
+        <v>449454</v>
       </c>
       <c r="R17" t="n">
-        <v>6720260</v>
+        <v>6720176</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2313,7 +2313,7 @@
         <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,37 +2416,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670771</v>
+        <v>127670094</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449600</v>
+        <v>449196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720158</v>
+        <v>6720173</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2498,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2517,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670000</v>
+        <v>127670771</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2555,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449159</v>
+        <v>449600</v>
       </c>
       <c r="R20" t="n">
-        <v>6720222</v>
+        <v>6720158</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2719,42 +2723,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670094</v>
+        <v>127670000</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2762,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449196</v>
+        <v>449159</v>
       </c>
       <c r="R22" t="n">
-        <v>6720173</v>
+        <v>6720222</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2806,6 +2805,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670849</v>
+        <v>127670032</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449556</v>
+        <v>449165</v>
       </c>
       <c r="R24" t="n">
-        <v>6720283</v>
+        <v>6720228</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670299</v>
+        <v>127670849</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449181</v>
+        <v>449556</v>
       </c>
       <c r="R25" t="n">
-        <v>6720023</v>
+        <v>6720283</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670032</v>
+        <v>127670299</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449165</v>
+        <v>449181</v>
       </c>
       <c r="R26" t="n">
-        <v>6720228</v>
+        <v>6720023</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127670556</v>
+        <v>127671155</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449417</v>
+        <v>449421</v>
       </c>
       <c r="R28" t="n">
-        <v>6720161</v>
+        <v>6720319</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3403,11 +3403,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3435,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127671155</v>
+        <v>127670556</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3446,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3473,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449421</v>
+        <v>449417</v>
       </c>
       <c r="R29" t="n">
-        <v>6720319</v>
+        <v>6720161</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3509,6 +3504,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>91338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R35" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4549,7 +4549,7 @@
         <v>127670266</v>
       </c>
       <c r="B40" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127670625</v>
+        <v>127671241</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449440</v>
+        <v>449445</v>
       </c>
       <c r="R41" t="n">
-        <v>6720118</v>
+        <v>6720188</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670448</v>
+        <v>127670625</v>
       </c>
       <c r="B42" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449292</v>
+        <v>449440</v>
       </c>
       <c r="R42" t="n">
-        <v>6720271</v>
+        <v>6720118</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671241</v>
+        <v>127670364</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449445</v>
+        <v>449245</v>
       </c>
       <c r="R43" t="n">
-        <v>6720188</v>
+        <v>6720058</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670364</v>
+        <v>127670593</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449245</v>
+        <v>449457</v>
       </c>
       <c r="R44" t="n">
-        <v>6720058</v>
+        <v>6720089</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670593</v>
+        <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449457</v>
+        <v>449202</v>
       </c>
       <c r="R45" t="n">
-        <v>6720089</v>
+        <v>6720026</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670309</v>
+        <v>127670448</v>
       </c>
       <c r="B46" t="n">
         <v>78779</v>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449202</v>
+        <v>449292</v>
       </c>
       <c r="R46" t="n">
-        <v>6720026</v>
+        <v>6720271</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670722</v>
+        <v>127670889</v>
       </c>
       <c r="B48" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449567</v>
+        <v>449605</v>
       </c>
       <c r="R48" t="n">
-        <v>6720141</v>
+        <v>6720315</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670889</v>
+        <v>127670168</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449605</v>
+        <v>449195</v>
       </c>
       <c r="R49" t="n">
-        <v>6720315</v>
+        <v>6720146</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670168</v>
+        <v>127670722</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449195</v>
+        <v>449567</v>
       </c>
       <c r="R50" t="n">
-        <v>6720146</v>
+        <v>6720141</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,46 +5661,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669856</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>56855</v>
+        <v>91338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5708,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449125</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720233</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5752,6 +5743,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5770,37 +5762,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B52" t="n">
-        <v>91332</v>
+        <v>56855</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5808,10 +5809,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R52" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5852,7 +5853,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670781</v>
+        <v>127670743</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449586</v>
+        <v>449576</v>
       </c>
       <c r="R60" t="n">
-        <v>6720154</v>
+        <v>6720141</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670743</v>
+        <v>127670781</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449576</v>
+        <v>449586</v>
       </c>
       <c r="R61" t="n">
-        <v>6720141</v>
+        <v>6720154</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670981</v>
+        <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449656</v>
+        <v>449210</v>
       </c>
       <c r="R63" t="n">
-        <v>6720358</v>
+        <v>6720149</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670152</v>
+        <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7020,10 +7020,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449210</v>
+        <v>449656</v>
       </c>
       <c r="R64" t="n">
-        <v>6720149</v>
+        <v>6720358</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670541</v>
+        <v>127669907</v>
       </c>
       <c r="B66" t="n">
-        <v>80123</v>
+        <v>78779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449410</v>
+        <v>449153</v>
       </c>
       <c r="R66" t="n">
-        <v>6720148</v>
+        <v>6720237</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7258,11 +7258,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7290,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127669907</v>
+        <v>127670953</v>
       </c>
       <c r="B67" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7301,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7328,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449153</v>
+        <v>449638</v>
       </c>
       <c r="R67" t="n">
-        <v>6720237</v>
+        <v>6720356</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7391,10 +7386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670953</v>
+        <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7402,21 +7397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7429,10 +7424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449638</v>
+        <v>449410</v>
       </c>
       <c r="R68" t="n">
-        <v>6720356</v>
+        <v>6720148</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7465,6 +7460,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670485</v>
+        <v>127670324</v>
       </c>
       <c r="B70" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7604,21 +7604,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449358</v>
+        <v>449217</v>
       </c>
       <c r="R70" t="n">
-        <v>6720139</v>
+        <v>6720024</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670324</v>
+        <v>127670825</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449217</v>
+        <v>449573</v>
       </c>
       <c r="R71" t="n">
-        <v>6720024</v>
+        <v>6720260</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670825</v>
+        <v>127670200</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449573</v>
+        <v>449202</v>
       </c>
       <c r="R72" t="n">
-        <v>6720260</v>
+        <v>6720096</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670200</v>
+        <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449202</v>
+        <v>449358</v>
       </c>
       <c r="R73" t="n">
-        <v>6720096</v>
+        <v>6720139</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670710</v>
+        <v>127670054</v>
       </c>
       <c r="B74" t="n">
-        <v>78779</v>
+        <v>91358</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,24 +8008,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8035,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449560</v>
+        <v>449185</v>
       </c>
       <c r="R74" t="n">
-        <v>6720133</v>
+        <v>6720192</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8300,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670054</v>
+        <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>91352</v>
+        <v>78779</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8311,28 +8315,24 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449185</v>
+        <v>449560</v>
       </c>
       <c r="R77" t="n">
-        <v>6720192</v>
+        <v>6720133</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127671164</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127670008</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,41 +877,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -921,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -965,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670907</v>
+        <v>127671038</v>
       </c>
       <c r="B5" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,28 +993,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1026,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449605</v>
+        <v>449628</v>
       </c>
       <c r="R5" t="n">
-        <v>6720348</v>
+        <v>6720382</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1089,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671175</v>
+        <v>127670618</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449421</v>
+        <v>449457</v>
       </c>
       <c r="R6" t="n">
-        <v>6720306</v>
+        <v>6720117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1193,7 +1187,7 @@
         <v>127670874</v>
       </c>
       <c r="B7" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127671038</v>
+        <v>127671175</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449628</v>
+        <v>449421</v>
       </c>
       <c r="R8" t="n">
-        <v>6720382</v>
+        <v>6720306</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1392,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670618</v>
+        <v>127670907</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,24 +1397,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1430,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449457</v>
+        <v>449605</v>
       </c>
       <c r="R9" t="n">
-        <v>6720117</v>
+        <v>6720348</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1493,40 +1491,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127670132</v>
+        <v>127671204</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449194</v>
+        <v>449443</v>
       </c>
       <c r="R13" t="n">
-        <v>6720159</v>
+        <v>6720234</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1901,10 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127671204</v>
+        <v>127670132</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449443</v>
+        <v>449194</v>
       </c>
       <c r="R14" t="n">
-        <v>6720234</v>
+        <v>6720159</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2002,37 +2002,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670513</v>
+        <v>127671090</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>98379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449366</v>
+        <v>449480</v>
       </c>
       <c r="R15" t="n">
-        <v>6720133</v>
+        <v>6720296</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2076,11 +2081,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,7 +2111,7 @@
         <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R17" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,6 +2283,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127671090</v>
+        <v>127671236</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449480</v>
+        <v>449454</v>
       </c>
       <c r="R18" t="n">
-        <v>6720296</v>
+        <v>6720176</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,42 +2416,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670094</v>
+        <v>127670000</v>
       </c>
       <c r="B19" t="n">
-        <v>56855</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449196</v>
+        <v>449159</v>
       </c>
       <c r="R19" t="n">
-        <v>6720173</v>
+        <v>6720222</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,6 +2498,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670771</v>
+        <v>127670496</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449600</v>
+        <v>449359</v>
       </c>
       <c r="R20" t="n">
-        <v>6720158</v>
+        <v>6720133</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2625,7 +2621,7 @@
         <v>127670476</v>
       </c>
       <c r="B21" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670000</v>
+        <v>127670771</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449159</v>
+        <v>449600</v>
       </c>
       <c r="R22" t="n">
-        <v>6720222</v>
+        <v>6720158</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2824,37 +2820,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670496</v>
+        <v>127670094</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>56858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2862,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449359</v>
+        <v>449196</v>
       </c>
       <c r="R23" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2906,7 +2907,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670032</v>
+        <v>127670299</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449165</v>
+        <v>449181</v>
       </c>
       <c r="R24" t="n">
-        <v>6720228</v>
+        <v>6720023</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670849</v>
+        <v>127670032</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449556</v>
+        <v>449165</v>
       </c>
       <c r="R25" t="n">
-        <v>6720283</v>
+        <v>6720228</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670299</v>
+        <v>127670849</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449181</v>
+        <v>449556</v>
       </c>
       <c r="R26" t="n">
-        <v>6720023</v>
+        <v>6720283</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3231,7 +3231,7 @@
         <v>127670118</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671155</v>
+        <v>127670556</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449421</v>
+        <v>449417</v>
       </c>
       <c r="R28" t="n">
-        <v>6720319</v>
+        <v>6720161</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3403,6 +3403,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3430,10 +3435,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127670556</v>
+        <v>127671155</v>
       </c>
       <c r="B29" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449417</v>
+        <v>449421</v>
       </c>
       <c r="R29" t="n">
-        <v>6720161</v>
+        <v>6720319</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3504,11 +3509,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3539,7 +3539,7 @@
         <v>127670217</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127670762</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>127671028</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127670445</v>
       </c>
       <c r="B34" t="n">
-        <v>91338</v>
+        <v>78782</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449296</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720275</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R35" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670445</v>
+        <v>127671216</v>
       </c>
       <c r="B37" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449296</v>
+        <v>449453</v>
       </c>
       <c r="R37" t="n">
-        <v>6720275</v>
+        <v>6720203</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4347,7 +4347,7 @@
         <v>127670341</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127670702</v>
       </c>
       <c r="B39" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>127670266</v>
       </c>
       <c r="B40" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671241</v>
+        <v>127670625</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449445</v>
+        <v>449440</v>
       </c>
       <c r="R41" t="n">
-        <v>6720188</v>
+        <v>6720118</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670625</v>
+        <v>127670593</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449440</v>
+        <v>449457</v>
       </c>
       <c r="R42" t="n">
-        <v>6720118</v>
+        <v>6720089</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670364</v>
+        <v>127671241</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449245</v>
+        <v>449445</v>
       </c>
       <c r="R43" t="n">
-        <v>6720058</v>
+        <v>6720188</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670593</v>
+        <v>127670364</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449457</v>
+        <v>449245</v>
       </c>
       <c r="R44" t="n">
-        <v>6720089</v>
+        <v>6720058</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5058,7 +5058,7 @@
         <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670889</v>
+        <v>127670722</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449605</v>
+        <v>449567</v>
       </c>
       <c r="R48" t="n">
-        <v>6720315</v>
+        <v>6720141</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670168</v>
+        <v>127670889</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449195</v>
+        <v>449605</v>
       </c>
       <c r="R49" t="n">
-        <v>6720146</v>
+        <v>6720315</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670722</v>
+        <v>127670168</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449567</v>
+        <v>449195</v>
       </c>
       <c r="R50" t="n">
-        <v>6720141</v>
+        <v>6720146</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127670649</v>
       </c>
       <c r="B51" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449438</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720136</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,46 +5762,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669856</v>
+        <v>127671143</v>
       </c>
       <c r="B52" t="n">
-        <v>56855</v>
+        <v>79023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5809,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449125</v>
+        <v>449435</v>
       </c>
       <c r="R52" t="n">
-        <v>6720233</v>
+        <v>6720323</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5853,6 +5844,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5871,10 +5863,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670754</v>
+        <v>127670921</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5909,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449589</v>
+        <v>449580</v>
       </c>
       <c r="R53" t="n">
-        <v>6720140</v>
+        <v>6720362</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,10 +5964,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670788</v>
+        <v>127671194</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5983,21 +5975,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6010,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449583</v>
+        <v>449456</v>
       </c>
       <c r="R54" t="n">
-        <v>6720169</v>
+        <v>6720223</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,10 +6065,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671143</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449435</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720323</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,10 +6166,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670649</v>
+        <v>127670788</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6212,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449438</v>
+        <v>449583</v>
       </c>
       <c r="R56" t="n">
-        <v>6720136</v>
+        <v>6720169</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,10 +6267,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670280</v>
+        <v>127670754</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6313,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449176</v>
+        <v>449589</v>
       </c>
       <c r="R57" t="n">
-        <v>6720013</v>
+        <v>6720140</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670921</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>56858</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449580</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720362</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670781</v>
+        <v>127671129</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449586</v>
+        <v>449427</v>
       </c>
       <c r="R61" t="n">
-        <v>6720154</v>
+        <v>6720322</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671129</v>
+        <v>127670781</v>
       </c>
       <c r="B62" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449427</v>
+        <v>449586</v>
       </c>
       <c r="R62" t="n">
-        <v>6720322</v>
+        <v>6720154</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6884,7 +6884,7 @@
         <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127669907</v>
+        <v>127670541</v>
       </c>
       <c r="B66" t="n">
-        <v>78779</v>
+        <v>80126</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449153</v>
+        <v>449410</v>
       </c>
       <c r="R66" t="n">
-        <v>6720237</v>
+        <v>6720148</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7258,6 +7258,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7285,10 +7290,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670953</v>
+        <v>127670605</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7323,10 +7328,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449638</v>
+        <v>449451</v>
       </c>
       <c r="R67" t="n">
-        <v>6720356</v>
+        <v>6720105</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7386,10 +7391,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B68" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7397,21 +7402,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7424,10 +7429,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R68" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7460,11 +7465,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670605</v>
+        <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449451</v>
+        <v>449153</v>
       </c>
       <c r="R69" t="n">
-        <v>6720105</v>
+        <v>6720237</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670324</v>
+        <v>127670825</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449217</v>
+        <v>449573</v>
       </c>
       <c r="R70" t="n">
-        <v>6720024</v>
+        <v>6720260</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670825</v>
+        <v>127670324</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449573</v>
+        <v>449217</v>
       </c>
       <c r="R71" t="n">
-        <v>6720260</v>
+        <v>6720024</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7798,7 +7798,7 @@
         <v>127670200</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670054</v>
+        <v>127671250</v>
       </c>
       <c r="B74" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,28 +8008,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8039,10 +8035,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449185</v>
+        <v>449429</v>
       </c>
       <c r="R74" t="n">
-        <v>6720192</v>
+        <v>6720186</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8102,10 +8098,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127671250</v>
+        <v>127670272</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8140,10 +8136,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449429</v>
+        <v>449168</v>
       </c>
       <c r="R75" t="n">
-        <v>6720186</v>
+        <v>6720012</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8203,10 +8199,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670272</v>
+        <v>127670054</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8214,24 +8210,28 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449168</v>
+        <v>449185</v>
       </c>
       <c r="R76" t="n">
-        <v>6720012</v>
+        <v>6720192</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8307,7 +8307,7 @@
         <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127671164</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127670008</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,40 +877,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R4" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -964,6 +965,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127671175</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449421</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720306</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670618</v>
+        <v>127670874</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449457</v>
+        <v>449564</v>
       </c>
       <c r="R6" t="n">
-        <v>6720117</v>
+        <v>6720313</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1184,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670874</v>
+        <v>127671038</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449564</v>
+        <v>449628</v>
       </c>
       <c r="R7" t="n">
-        <v>6720313</v>
+        <v>6720382</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1285,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127671175</v>
+        <v>127670618</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449421</v>
+        <v>449457</v>
       </c>
       <c r="R8" t="n">
-        <v>6720306</v>
+        <v>6720117</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1389,7 +1391,7 @@
         <v>127670907</v>
       </c>
       <c r="B9" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,41 +1493,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127671204</v>
+        <v>127670132</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449443</v>
+        <v>449194</v>
       </c>
       <c r="R13" t="n">
-        <v>6720234</v>
+        <v>6720159</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1901,10 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127670132</v>
+        <v>127671204</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449194</v>
+        <v>449443</v>
       </c>
       <c r="R14" t="n">
-        <v>6720159</v>
+        <v>6720234</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2002,42 +2002,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127671090</v>
+        <v>127670513</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449480</v>
+        <v>449366</v>
       </c>
       <c r="R15" t="n">
-        <v>6720296</v>
+        <v>6720133</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2081,6 +2076,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,7 +2111,7 @@
         <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R17" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,11 +2283,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127671236</v>
+        <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>98387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449454</v>
+        <v>449480</v>
       </c>
       <c r="R18" t="n">
-        <v>6720176</v>
+        <v>6720296</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670000</v>
+        <v>127670771</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449159</v>
+        <v>449600</v>
       </c>
       <c r="R19" t="n">
-        <v>6720222</v>
+        <v>6720158</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670496</v>
+        <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>78782</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449359</v>
+        <v>449363</v>
       </c>
       <c r="R20" t="n">
-        <v>6720133</v>
+        <v>6720137</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670476</v>
+        <v>127670000</v>
       </c>
       <c r="B21" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449363</v>
+        <v>449159</v>
       </c>
       <c r="R21" t="n">
-        <v>6720137</v>
+        <v>6720222</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670771</v>
+        <v>127670496</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449600</v>
+        <v>449359</v>
       </c>
       <c r="R22" t="n">
-        <v>6720158</v>
+        <v>6720133</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2823,7 +2823,7 @@
         <v>127670094</v>
       </c>
       <c r="B23" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670299</v>
+        <v>127670032</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449181</v>
+        <v>449165</v>
       </c>
       <c r="R24" t="n">
-        <v>6720023</v>
+        <v>6720228</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670032</v>
+        <v>127670849</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449165</v>
+        <v>449556</v>
       </c>
       <c r="R25" t="n">
-        <v>6720228</v>
+        <v>6720283</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670849</v>
+        <v>127670299</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449556</v>
+        <v>449181</v>
       </c>
       <c r="R26" t="n">
-        <v>6720283</v>
+        <v>6720023</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3231,7 +3231,7 @@
         <v>127670118</v>
       </c>
       <c r="B27" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127670556</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>80126</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449417</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720161</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3403,11 +3403,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3438,7 +3433,7 @@
         <v>127671155</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3536,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670217</v>
+        <v>127670556</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>80132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3542,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3574,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449200</v>
+        <v>449417</v>
       </c>
       <c r="R30" t="n">
-        <v>6720125</v>
+        <v>6720161</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3610,6 +3605,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670762</v>
+        <v>127670217</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449570</v>
+        <v>449200</v>
       </c>
       <c r="R31" t="n">
-        <v>6720155</v>
+        <v>6720125</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3738,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127671028</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449628</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720374</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B33" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670445</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>78782</v>
+        <v>91349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449296</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720275</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671216</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449453</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720203</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671229</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449442</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720178</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127671216</v>
+        <v>127670445</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449453</v>
+        <v>449296</v>
       </c>
       <c r="R37" t="n">
-        <v>6720203</v>
+        <v>6720275</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4347,7 +4347,7 @@
         <v>127670341</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4445,35 +4445,39 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127670702</v>
+        <v>127670266</v>
       </c>
       <c r="B39" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4483,10 +4487,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449550</v>
+        <v>449176</v>
       </c>
       <c r="R39" t="n">
-        <v>6720131</v>
+        <v>6720025</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4546,39 +4550,35 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127670266</v>
+        <v>127670702</v>
       </c>
       <c r="B40" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449176</v>
+        <v>449550</v>
       </c>
       <c r="R40" t="n">
-        <v>6720025</v>
+        <v>6720131</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127670625</v>
+        <v>127671241</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449440</v>
+        <v>449445</v>
       </c>
       <c r="R41" t="n">
-        <v>6720118</v>
+        <v>6720188</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670593</v>
+        <v>127670625</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449457</v>
+        <v>449440</v>
       </c>
       <c r="R42" t="n">
-        <v>6720089</v>
+        <v>6720118</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671241</v>
+        <v>127670364</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449445</v>
+        <v>449245</v>
       </c>
       <c r="R43" t="n">
-        <v>6720188</v>
+        <v>6720058</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670364</v>
+        <v>127670593</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449245</v>
+        <v>449457</v>
       </c>
       <c r="R44" t="n">
-        <v>6720058</v>
+        <v>6720089</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5058,7 +5058,7 @@
         <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670722</v>
+        <v>127670889</v>
       </c>
       <c r="B48" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449567</v>
+        <v>449605</v>
       </c>
       <c r="R48" t="n">
-        <v>6720141</v>
+        <v>6720315</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670889</v>
+        <v>127670168</v>
       </c>
       <c r="B49" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449605</v>
+        <v>449195</v>
       </c>
       <c r="R49" t="n">
-        <v>6720315</v>
+        <v>6720146</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670168</v>
+        <v>127670722</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449195</v>
+        <v>449567</v>
       </c>
       <c r="R50" t="n">
-        <v>6720146</v>
+        <v>6720141</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670649</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449438</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720136</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671143</v>
+        <v>127670754</v>
       </c>
       <c r="B52" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449435</v>
+        <v>449589</v>
       </c>
       <c r="R52" t="n">
-        <v>6720323</v>
+        <v>6720140</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,10 +5863,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670921</v>
+        <v>127670788</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449580</v>
+        <v>449583</v>
       </c>
       <c r="R53" t="n">
-        <v>6720362</v>
+        <v>6720169</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,10 +5964,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671194</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5975,21 +5975,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449456</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720223</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670788</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449583</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720169</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670754</v>
+        <v>127670921</v>
       </c>
       <c r="B57" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449589</v>
+        <v>449580</v>
       </c>
       <c r="R57" t="n">
-        <v>6720140</v>
+        <v>6720362</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6371,7 +6371,7 @@
         <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671129</v>
+        <v>127670781</v>
       </c>
       <c r="B61" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449427</v>
+        <v>449586</v>
       </c>
       <c r="R61" t="n">
-        <v>6720322</v>
+        <v>6720154</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670781</v>
+        <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449586</v>
+        <v>449427</v>
       </c>
       <c r="R62" t="n">
-        <v>6720154</v>
+        <v>6720322</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6884,7 +6884,7 @@
         <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B66" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R66" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7258,11 +7258,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7290,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>80132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7301,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7328,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R67" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7364,6 +7359,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7391,10 +7391,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670953</v>
+        <v>127670605</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7429,10 +7429,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449638</v>
+        <v>449451</v>
       </c>
       <c r="R68" t="n">
-        <v>6720356</v>
+        <v>6720105</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7495,7 +7495,7 @@
         <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670825</v>
+        <v>127670324</v>
       </c>
       <c r="B70" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449573</v>
+        <v>449217</v>
       </c>
       <c r="R70" t="n">
-        <v>6720260</v>
+        <v>6720024</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670324</v>
+        <v>127670825</v>
       </c>
       <c r="B71" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449217</v>
+        <v>449573</v>
       </c>
       <c r="R71" t="n">
-        <v>6720024</v>
+        <v>6720260</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7798,7 +7798,7 @@
         <v>127670200</v>
       </c>
       <c r="B72" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127671250</v>
       </c>
       <c r="B74" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>127670272</v>
       </c>
       <c r="B75" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>127670054</v>
       </c>
       <c r="B76" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127671175</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449421</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720306</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -984,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671175</v>
+        <v>127671038</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1022,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R5" t="n">
-        <v>6720306</v>
+        <v>6720382</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1085,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670874</v>
+        <v>127670618</v>
       </c>
       <c r="B6" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449564</v>
+        <v>449457</v>
       </c>
       <c r="R6" t="n">
-        <v>6720313</v>
+        <v>6720117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1186,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671038</v>
+        <v>127670907</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,24 +1191,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1224,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R7" t="n">
-        <v>6720382</v>
+        <v>6720348</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670618</v>
+        <v>127670574</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,26 +1296,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449457</v>
+        <v>449419</v>
       </c>
       <c r="R8" t="n">
-        <v>6720117</v>
+        <v>6720156</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1369,7 +1372,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1388,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670907</v>
+        <v>127670874</v>
       </c>
       <c r="B9" t="n">
-        <v>91369</v>
+        <v>78787</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,28 +1401,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1430,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449605</v>
+        <v>449564</v>
       </c>
       <c r="R9" t="n">
-        <v>6720348</v>
+        <v>6720313</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1493,40 +1491,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,37 +2002,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670513</v>
+        <v>127671090</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>98388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449366</v>
+        <v>449480</v>
       </c>
       <c r="R15" t="n">
-        <v>6720133</v>
+        <v>6720296</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2076,11 +2081,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670838</v>
+        <v>127671236</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449579</v>
+        <v>449454</v>
       </c>
       <c r="R16" t="n">
-        <v>6720260</v>
+        <v>6720176</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R17" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,6 +2283,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127671090</v>
+        <v>127670838</v>
       </c>
       <c r="B18" t="n">
-        <v>98387</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223597</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449480</v>
+        <v>449579</v>
       </c>
       <c r="R18" t="n">
-        <v>6720296</v>
+        <v>6720260</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,37 +2416,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670771</v>
+        <v>127670094</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449600</v>
+        <v>449196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720158</v>
+        <v>6720173</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2498,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2517,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670476</v>
+        <v>127670771</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449363</v>
+        <v>449600</v>
       </c>
       <c r="R20" t="n">
-        <v>6720137</v>
+        <v>6720158</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2719,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670496</v>
+        <v>127670476</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,21 +2734,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449359</v>
+        <v>449363</v>
       </c>
       <c r="R22" t="n">
-        <v>6720133</v>
+        <v>6720137</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2820,42 +2824,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670094</v>
+        <v>127670496</v>
       </c>
       <c r="B23" t="n">
-        <v>56864</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2863,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449196</v>
+        <v>449359</v>
       </c>
       <c r="R23" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2907,6 +2906,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670556</v>
+        <v>127670217</v>
       </c>
       <c r="B30" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449417</v>
+        <v>449200</v>
       </c>
       <c r="R30" t="n">
-        <v>6720161</v>
+        <v>6720125</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3605,11 +3605,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,7 +3632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670217</v>
+        <v>127670762</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3675,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449200</v>
+        <v>449570</v>
       </c>
       <c r="R31" t="n">
-        <v>6720125</v>
+        <v>6720155</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3738,7 +3733,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127671028</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449628</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720374</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3839,10 +3834,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127671028</v>
+        <v>127670556</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3845,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449628</v>
+        <v>449417</v>
       </c>
       <c r="R33" t="n">
-        <v>6720374</v>
+        <v>6720161</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3913,6 +3908,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B34" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R35" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4448,7 +4448,7 @@
         <v>127670266</v>
       </c>
       <c r="B39" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5661,37 +5661,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B51" t="n">
-        <v>91349</v>
+        <v>56864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5699,10 +5708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5743,7 +5752,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670754</v>
+        <v>127671194</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5808,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449589</v>
+        <v>449456</v>
       </c>
       <c r="R52" t="n">
-        <v>6720140</v>
+        <v>6720223</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5871,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670788</v>
+        <v>127670754</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5901,10 +5909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449583</v>
+        <v>449589</v>
       </c>
       <c r="R53" t="n">
-        <v>6720169</v>
+        <v>6720140</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670788</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6002,10 +6010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449583</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720169</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6073,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6103,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R55" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6174,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6204,10 +6212,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,7 +6275,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670921</v>
+        <v>127670280</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449580</v>
+        <v>449176</v>
       </c>
       <c r="R57" t="n">
-        <v>6720362</v>
+        <v>6720013</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127670921</v>
       </c>
       <c r="B58" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449580</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720362</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670181</v>
+        <v>127671129</v>
       </c>
       <c r="B59" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449202</v>
+        <v>449427</v>
       </c>
       <c r="R59" t="n">
-        <v>6720148</v>
+        <v>6720322</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671129</v>
+        <v>127670181</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449427</v>
+        <v>449202</v>
       </c>
       <c r="R62" t="n">
-        <v>6720322</v>
+        <v>6720148</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670541</v>
+        <v>127670605</v>
       </c>
       <c r="B67" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449410</v>
+        <v>449451</v>
       </c>
       <c r="R67" t="n">
-        <v>6720148</v>
+        <v>6720105</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,11 +7359,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7391,10 +7386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7402,21 +7397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7429,10 +7424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R68" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7465,6 +7460,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670324</v>
+        <v>127670485</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7604,21 +7604,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449217</v>
+        <v>449358</v>
       </c>
       <c r="R70" t="n">
-        <v>6720024</v>
+        <v>6720139</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670825</v>
+        <v>127670324</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449573</v>
+        <v>449217</v>
       </c>
       <c r="R71" t="n">
-        <v>6720260</v>
+        <v>6720024</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670200</v>
+        <v>127670825</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449202</v>
+        <v>449573</v>
       </c>
       <c r="R72" t="n">
-        <v>6720096</v>
+        <v>6720260</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670485</v>
+        <v>127670200</v>
       </c>
       <c r="B73" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449358</v>
+        <v>449202</v>
       </c>
       <c r="R73" t="n">
-        <v>6720139</v>
+        <v>6720096</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8202,7 +8202,7 @@
         <v>127670054</v>
       </c>
       <c r="B76" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,37 +877,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671175</v>
+        <v>127671018</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449421</v>
+        <v>449633</v>
       </c>
       <c r="R4" t="n">
-        <v>6720306</v>
+        <v>6720378</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,7 +984,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127671175</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1016,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449421</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720306</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670618</v>
+        <v>127670874</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449457</v>
+        <v>449564</v>
       </c>
       <c r="R6" t="n">
-        <v>6720117</v>
+        <v>6720313</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670907</v>
+        <v>127671038</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,28 +1197,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1222,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449605</v>
+        <v>449628</v>
       </c>
       <c r="R7" t="n">
-        <v>6720348</v>
+        <v>6720382</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1285,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670574</v>
+        <v>127670618</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,31 +1298,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1328,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449419</v>
+        <v>449457</v>
       </c>
       <c r="R8" t="n">
-        <v>6720156</v>
+        <v>6720117</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1372,6 +1369,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670874</v>
+        <v>127670907</v>
       </c>
       <c r="B9" t="n">
-        <v>78787</v>
+        <v>91370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,24 +1399,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1428,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449564</v>
+        <v>449605</v>
       </c>
       <c r="R9" t="n">
-        <v>6720313</v>
+        <v>6720348</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,41 +1493,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,42 +2002,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127671090</v>
+        <v>127670513</v>
       </c>
       <c r="B15" t="n">
-        <v>98388</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449480</v>
+        <v>449366</v>
       </c>
       <c r="R15" t="n">
-        <v>6720296</v>
+        <v>6720133</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2081,6 +2076,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127671236</v>
+        <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449454</v>
+        <v>449579</v>
       </c>
       <c r="R16" t="n">
-        <v>6720176</v>
+        <v>6720260</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R17" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,11 +2283,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670838</v>
+        <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>98388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>223597</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449579</v>
+        <v>449480</v>
       </c>
       <c r="R18" t="n">
-        <v>6720260</v>
+        <v>6720296</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,42 +2416,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670094</v>
+        <v>127670771</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449196</v>
+        <v>449600</v>
       </c>
       <c r="R19" t="n">
-        <v>6720173</v>
+        <v>6720158</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,6 +2498,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670771</v>
+        <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449600</v>
+        <v>449363</v>
       </c>
       <c r="R20" t="n">
-        <v>6720158</v>
+        <v>6720137</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2723,37 +2719,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670476</v>
+        <v>127670094</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449363</v>
+        <v>449196</v>
       </c>
       <c r="R22" t="n">
-        <v>6720137</v>
+        <v>6720173</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2805,7 +2806,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127671155</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449421</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720319</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127671155</v>
+        <v>127670556</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449421</v>
+        <v>449417</v>
       </c>
       <c r="R29" t="n">
-        <v>6720319</v>
+        <v>6720161</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3504,6 +3504,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670556</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>80132</v>
+        <v>78788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3845,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3872,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449417</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720161</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3908,11 +3913,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671216</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449453</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720203</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671216</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449453</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720203</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671229</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449442</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720178</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671241</v>
+        <v>127670309</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4662,21 +4662,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449445</v>
+        <v>449202</v>
       </c>
       <c r="R41" t="n">
-        <v>6720188</v>
+        <v>6720026</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670625</v>
+        <v>127670448</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449440</v>
+        <v>449292</v>
       </c>
       <c r="R42" t="n">
-        <v>6720118</v>
+        <v>6720271</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670364</v>
+        <v>127671241</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449245</v>
+        <v>449445</v>
       </c>
       <c r="R43" t="n">
-        <v>6720058</v>
+        <v>6720188</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670593</v>
+        <v>127670625</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449457</v>
+        <v>449440</v>
       </c>
       <c r="R44" t="n">
-        <v>6720089</v>
+        <v>6720118</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670309</v>
+        <v>127670364</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449202</v>
+        <v>449245</v>
       </c>
       <c r="R45" t="n">
-        <v>6720026</v>
+        <v>6720058</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670448</v>
+        <v>127670593</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5167,21 +5167,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449292</v>
+        <v>449457</v>
       </c>
       <c r="R46" t="n">
-        <v>6720271</v>
+        <v>6720089</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5661,46 +5661,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669856</v>
+        <v>127670754</v>
       </c>
       <c r="B51" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5708,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449125</v>
+        <v>449589</v>
       </c>
       <c r="R51" t="n">
-        <v>6720233</v>
+        <v>6720140</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5752,6 +5743,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671194</v>
+        <v>127670788</v>
       </c>
       <c r="B52" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5808,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449456</v>
+        <v>449583</v>
       </c>
       <c r="R52" t="n">
-        <v>6720223</v>
+        <v>6720169</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5871,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670754</v>
+        <v>127671143</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5909,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449589</v>
+        <v>449435</v>
       </c>
       <c r="R53" t="n">
-        <v>6720140</v>
+        <v>6720323</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670788</v>
+        <v>127670649</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6010,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449583</v>
+        <v>449438</v>
       </c>
       <c r="R54" t="n">
-        <v>6720169</v>
+        <v>6720136</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671143</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6111,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449435</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720323</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670649</v>
+        <v>127670921</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6212,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449438</v>
+        <v>449580</v>
       </c>
       <c r="R56" t="n">
-        <v>6720136</v>
+        <v>6720362</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,37 +6267,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670280</v>
+        <v>127669856</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6313,10 +6314,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449176</v>
+        <v>449125</v>
       </c>
       <c r="R57" t="n">
-        <v>6720013</v>
+        <v>6720233</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6357,7 +6358,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6376,10 +6376,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670921</v>
+        <v>127671194</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449580</v>
+        <v>449456</v>
       </c>
       <c r="R58" t="n">
-        <v>6720362</v>
+        <v>6720223</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671129</v>
+        <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449427</v>
+        <v>449202</v>
       </c>
       <c r="R59" t="n">
-        <v>6720322</v>
+        <v>6720148</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670181</v>
+        <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449202</v>
+        <v>449427</v>
       </c>
       <c r="R62" t="n">
-        <v>6720148</v>
+        <v>6720322</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R67" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,6 +7359,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7386,10 +7391,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670541</v>
+        <v>127670605</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7397,21 +7402,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7424,10 +7429,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449410</v>
+        <v>449451</v>
       </c>
       <c r="R68" t="n">
-        <v>6720148</v>
+        <v>6720105</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7460,11 +7465,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670485</v>
+        <v>127670324</v>
       </c>
       <c r="B70" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7604,21 +7604,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449358</v>
+        <v>449217</v>
       </c>
       <c r="R70" t="n">
-        <v>6720139</v>
+        <v>6720024</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670324</v>
+        <v>127670825</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449217</v>
+        <v>449573</v>
       </c>
       <c r="R71" t="n">
-        <v>6720024</v>
+        <v>6720260</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670825</v>
+        <v>127670200</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449573</v>
+        <v>449202</v>
       </c>
       <c r="R72" t="n">
-        <v>6720260</v>
+        <v>6720096</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670200</v>
+        <v>127670485</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449202</v>
+        <v>449358</v>
       </c>
       <c r="R73" t="n">
-        <v>6720096</v>
+        <v>6720139</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127671164</v>
+        <v>127670008</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449428</v>
+        <v>449167</v>
       </c>
       <c r="R2" t="n">
-        <v>6720312</v>
+        <v>6720240</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127670008</v>
+        <v>127671164</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449167</v>
+        <v>449428</v>
       </c>
       <c r="R3" t="n">
-        <v>6720240</v>
+        <v>6720312</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,41 +877,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -921,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -965,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671175</v>
+        <v>127670907</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,24 +993,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1022,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449421</v>
+        <v>449605</v>
       </c>
       <c r="R5" t="n">
-        <v>6720306</v>
+        <v>6720348</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1085,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670874</v>
+        <v>127671175</v>
       </c>
       <c r="B6" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449564</v>
+        <v>449421</v>
       </c>
       <c r="R6" t="n">
-        <v>6720313</v>
+        <v>6720306</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1186,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671038</v>
+        <v>127670874</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449628</v>
+        <v>449564</v>
       </c>
       <c r="R7" t="n">
-        <v>6720382</v>
+        <v>6720313</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670618</v>
+        <v>127671038</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1325,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449457</v>
+        <v>449628</v>
       </c>
       <c r="R8" t="n">
-        <v>6720117</v>
+        <v>6720382</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1388,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670907</v>
+        <v>127670618</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,28 +1401,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1430,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449605</v>
+        <v>449457</v>
       </c>
       <c r="R9" t="n">
-        <v>6720348</v>
+        <v>6720117</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1493,40 +1491,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670513</v>
+        <v>127670838</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449366</v>
+        <v>449579</v>
       </c>
       <c r="R15" t="n">
-        <v>6720133</v>
+        <v>6720260</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2076,11 +2076,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670838</v>
+        <v>127670513</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449579</v>
+        <v>449366</v>
       </c>
       <c r="R16" t="n">
-        <v>6720260</v>
+        <v>6720133</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2182,6 +2177,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,7 +2313,7 @@
         <v>127671090</v>
       </c>
       <c r="B18" t="n">
-        <v>98388</v>
+        <v>98389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670771</v>
+        <v>127670496</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449600</v>
+        <v>449359</v>
       </c>
       <c r="R19" t="n">
-        <v>6720158</v>
+        <v>6720133</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2719,42 +2719,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670094</v>
+        <v>127670771</v>
       </c>
       <c r="B22" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2762,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449196</v>
+        <v>449600</v>
       </c>
       <c r="R22" t="n">
-        <v>6720173</v>
+        <v>6720158</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2806,6 +2801,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,37 +2820,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670496</v>
+        <v>127670094</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2862,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449359</v>
+        <v>449196</v>
       </c>
       <c r="R23" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2906,7 +2907,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670032</v>
+        <v>127670118</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449165</v>
+        <v>449175</v>
       </c>
       <c r="R24" t="n">
-        <v>6720228</v>
+        <v>6720175</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670849</v>
+        <v>127670032</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449556</v>
+        <v>449165</v>
       </c>
       <c r="R25" t="n">
-        <v>6720283</v>
+        <v>6720228</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670299</v>
+        <v>127670849</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449181</v>
+        <v>449556</v>
       </c>
       <c r="R26" t="n">
-        <v>6720023</v>
+        <v>6720283</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670118</v>
+        <v>127670299</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449175</v>
+        <v>449181</v>
       </c>
       <c r="R27" t="n">
-        <v>6720175</v>
+        <v>6720023</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R35" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4448,7 +4448,7 @@
         <v>127670266</v>
       </c>
       <c r="B39" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127670309</v>
+        <v>127671241</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4662,21 +4662,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449202</v>
+        <v>449445</v>
       </c>
       <c r="R41" t="n">
-        <v>6720026</v>
+        <v>6720188</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670448</v>
+        <v>127670625</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449292</v>
+        <v>449440</v>
       </c>
       <c r="R42" t="n">
-        <v>6720271</v>
+        <v>6720118</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671241</v>
+        <v>127670364</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449445</v>
+        <v>449245</v>
       </c>
       <c r="R43" t="n">
-        <v>6720188</v>
+        <v>6720058</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670625</v>
+        <v>127670593</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449440</v>
+        <v>449457</v>
       </c>
       <c r="R44" t="n">
-        <v>6720118</v>
+        <v>6720089</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670364</v>
+        <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449245</v>
+        <v>449202</v>
       </c>
       <c r="R45" t="n">
-        <v>6720058</v>
+        <v>6720026</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670593</v>
+        <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5167,21 +5167,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449457</v>
+        <v>449292</v>
       </c>
       <c r="R46" t="n">
-        <v>6720089</v>
+        <v>6720271</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670921</v>
+        <v>127671194</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449580</v>
+        <v>449456</v>
       </c>
       <c r="R56" t="n">
-        <v>6720362</v>
+        <v>6720223</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,46 +6267,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127669856</v>
+        <v>127670921</v>
       </c>
       <c r="B57" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6314,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449125</v>
+        <v>449580</v>
       </c>
       <c r="R57" t="n">
-        <v>6720233</v>
+        <v>6720362</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6358,6 +6349,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>91350</v>
+        <v>56864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670181</v>
+        <v>127671129</v>
       </c>
       <c r="B59" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449202</v>
+        <v>449427</v>
       </c>
       <c r="R59" t="n">
-        <v>6720148</v>
+        <v>6720322</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670743</v>
+        <v>127670181</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449576</v>
+        <v>449202</v>
       </c>
       <c r="R60" t="n">
-        <v>6720141</v>
+        <v>6720148</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670781</v>
+        <v>127670743</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449586</v>
+        <v>449576</v>
       </c>
       <c r="R61" t="n">
-        <v>6720154</v>
+        <v>6720141</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671129</v>
+        <v>127670781</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449427</v>
+        <v>449586</v>
       </c>
       <c r="R62" t="n">
-        <v>6720322</v>
+        <v>6720154</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -8098,10 +8098,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670272</v>
+        <v>127670054</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>91371</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8109,24 +8109,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -8136,10 +8140,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449168</v>
+        <v>449185</v>
       </c>
       <c r="R75" t="n">
-        <v>6720012</v>
+        <v>6720192</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8199,10 +8203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670054</v>
+        <v>127670272</v>
       </c>
       <c r="B76" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8210,28 +8214,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449185</v>
+        <v>449168</v>
       </c>
       <c r="R76" t="n">
-        <v>6720192</v>
+        <v>6720012</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,40 +877,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670574</v>
+        <v>127671018</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449419</v>
+        <v>449633</v>
       </c>
       <c r="R4" t="n">
-        <v>6720156</v>
+        <v>6720378</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -964,6 +965,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670907</v>
+        <v>127671175</v>
       </c>
       <c r="B5" t="n">
-        <v>91371</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,28 +995,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1024,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449605</v>
+        <v>449421</v>
       </c>
       <c r="R5" t="n">
-        <v>6720348</v>
+        <v>6720306</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1087,7 +1085,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671175</v>
+        <v>127671038</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1125,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R6" t="n">
-        <v>6720306</v>
+        <v>6720382</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1188,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670874</v>
+        <v>127670618</v>
       </c>
       <c r="B7" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449564</v>
+        <v>449457</v>
       </c>
       <c r="R7" t="n">
-        <v>6720313</v>
+        <v>6720117</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1289,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127671038</v>
+        <v>127670907</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,24 +1298,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1327,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R8" t="n">
-        <v>6720382</v>
+        <v>6720348</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1390,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670618</v>
+        <v>127670874</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449457</v>
+        <v>449564</v>
       </c>
       <c r="R9" t="n">
-        <v>6720117</v>
+        <v>6720313</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,41 +1493,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670574</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449419</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720156</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1579,7 +1580,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R11" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R12" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2002,37 +2002,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670838</v>
+        <v>127671090</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>98390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>223597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449579</v>
+        <v>449480</v>
       </c>
       <c r="R15" t="n">
-        <v>6720260</v>
+        <v>6720296</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R16" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2177,11 +2182,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R17" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,6 +2283,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127671090</v>
+        <v>127670838</v>
       </c>
       <c r="B18" t="n">
-        <v>98389</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223597</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449480</v>
+        <v>449579</v>
       </c>
       <c r="R18" t="n">
-        <v>6720296</v>
+        <v>6720260</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,37 +2416,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670496</v>
+        <v>127670094</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449359</v>
+        <v>449196</v>
       </c>
       <c r="R19" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2498,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2517,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670476</v>
+        <v>127670771</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449363</v>
+        <v>449600</v>
       </c>
       <c r="R20" t="n">
-        <v>6720137</v>
+        <v>6720158</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2719,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670771</v>
+        <v>127670476</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,21 +2734,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449600</v>
+        <v>449363</v>
       </c>
       <c r="R22" t="n">
-        <v>6720158</v>
+        <v>6720137</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2820,42 +2824,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670094</v>
+        <v>127670496</v>
       </c>
       <c r="B23" t="n">
-        <v>56864</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2863,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449196</v>
+        <v>449359</v>
       </c>
       <c r="R23" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2907,6 +2906,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670118</v>
+        <v>127670849</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449175</v>
+        <v>449556</v>
       </c>
       <c r="R24" t="n">
-        <v>6720175</v>
+        <v>6720283</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670849</v>
+        <v>127670299</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449556</v>
+        <v>449181</v>
       </c>
       <c r="R26" t="n">
-        <v>6720283</v>
+        <v>6720023</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670299</v>
+        <v>127670118</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449181</v>
+        <v>449175</v>
       </c>
       <c r="R27" t="n">
-        <v>6720023</v>
+        <v>6720175</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671155</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449421</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720319</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127670556</v>
+        <v>127671155</v>
       </c>
       <c r="B29" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449417</v>
+        <v>449421</v>
       </c>
       <c r="R29" t="n">
-        <v>6720161</v>
+        <v>6720319</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3504,11 +3504,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3637,7 +3632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670762</v>
+        <v>127671028</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3675,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449570</v>
+        <v>449628</v>
       </c>
       <c r="R31" t="n">
-        <v>6720155</v>
+        <v>6720374</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3738,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127671028</v>
+        <v>127670556</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3744,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449628</v>
+        <v>449417</v>
       </c>
       <c r="R32" t="n">
-        <v>6720374</v>
+        <v>6720161</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3812,6 +3807,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127670762</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449570</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720155</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4145,7 +4145,7 @@
         <v>127671229</v>
       </c>
       <c r="B36" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>127670266</v>
       </c>
       <c r="B39" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670754</v>
+        <v>127670788</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449589</v>
+        <v>449583</v>
       </c>
       <c r="R51" t="n">
-        <v>6720140</v>
+        <v>6720169</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670788</v>
+        <v>127671194</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449583</v>
+        <v>449456</v>
       </c>
       <c r="R52" t="n">
-        <v>6720169</v>
+        <v>6720223</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671143</v>
+        <v>127670754</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449435</v>
+        <v>449589</v>
       </c>
       <c r="R53" t="n">
-        <v>6720323</v>
+        <v>6720140</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670649</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449438</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720136</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,10 +6166,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671194</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449456</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720223</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671129</v>
+        <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449427</v>
+        <v>449202</v>
       </c>
       <c r="R59" t="n">
-        <v>6720322</v>
+        <v>6720148</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670181</v>
+        <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449202</v>
+        <v>449576</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720141</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670743</v>
+        <v>127670781</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449576</v>
+        <v>449586</v>
       </c>
       <c r="R61" t="n">
-        <v>6720141</v>
+        <v>6720154</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670781</v>
+        <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449586</v>
+        <v>449427</v>
       </c>
       <c r="R62" t="n">
-        <v>6720154</v>
+        <v>6720322</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670152</v>
+        <v>127670731</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449210</v>
+        <v>449569</v>
       </c>
       <c r="R63" t="n">
-        <v>6720149</v>
+        <v>6720138</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670981</v>
+        <v>127670152</v>
       </c>
       <c r="B64" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7020,10 +7020,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449656</v>
+        <v>449210</v>
       </c>
       <c r="R64" t="n">
-        <v>6720358</v>
+        <v>6720149</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127670731</v>
+        <v>127670981</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>79647</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,21 +7094,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449569</v>
+        <v>449656</v>
       </c>
       <c r="R65" t="n">
-        <v>6720138</v>
+        <v>6720358</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7184,7 +7184,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670953</v>
+        <v>127670605</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449638</v>
+        <v>449451</v>
       </c>
       <c r="R66" t="n">
-        <v>6720356</v>
+        <v>6720105</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B67" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R67" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,11 +7359,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7391,10 +7386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7402,21 +7397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7429,10 +7424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R68" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7465,6 +7460,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7694,7 +7694,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670825</v>
+        <v>127670200</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449573</v>
+        <v>449202</v>
       </c>
       <c r="R71" t="n">
-        <v>6720260</v>
+        <v>6720096</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670200</v>
+        <v>127670825</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449202</v>
+        <v>449573</v>
       </c>
       <c r="R72" t="n">
-        <v>6720096</v>
+        <v>6720260</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671250</v>
+        <v>127670710</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,21 +8008,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449429</v>
+        <v>449560</v>
       </c>
       <c r="R74" t="n">
-        <v>6720186</v>
+        <v>6720133</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8101,7 +8101,7 @@
         <v>127670054</v>
       </c>
       <c r="B75" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670272</v>
+        <v>127671250</v>
       </c>
       <c r="B76" t="n">
         <v>79029</v>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449168</v>
+        <v>449429</v>
       </c>
       <c r="R76" t="n">
-        <v>6720012</v>
+        <v>6720186</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670710</v>
+        <v>127670272</v>
       </c>
       <c r="B77" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449560</v>
+        <v>449168</v>
       </c>
       <c r="R77" t="n">
-        <v>6720133</v>
+        <v>6720012</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127670008</v>
+        <v>127671164</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449167</v>
+        <v>449428</v>
       </c>
       <c r="R2" t="n">
-        <v>6720240</v>
+        <v>6720312</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127671164</v>
+        <v>127670008</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449428</v>
+        <v>449167</v>
       </c>
       <c r="R3" t="n">
-        <v>6720312</v>
+        <v>6720240</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,43 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671018</v>
+        <v>127671175</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -921,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449633</v>
+        <v>449421</v>
       </c>
       <c r="R4" t="n">
-        <v>6720378</v>
+        <v>6720306</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -984,7 +978,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671175</v>
+        <v>127671038</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1022,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R5" t="n">
-        <v>6720306</v>
+        <v>6720382</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1085,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671038</v>
+        <v>127670618</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1123,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449628</v>
+        <v>449457</v>
       </c>
       <c r="R6" t="n">
-        <v>6720382</v>
+        <v>6720117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1186,37 +1180,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670618</v>
+        <v>127671018</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449457</v>
+        <v>449633</v>
       </c>
       <c r="R7" t="n">
-        <v>6720117</v>
+        <v>6720378</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670907</v>
+        <v>127670574</v>
       </c>
       <c r="B8" t="n">
-        <v>91372</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,30 +1298,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1329,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449605</v>
+        <v>449419</v>
       </c>
       <c r="R8" t="n">
-        <v>6720348</v>
+        <v>6720156</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1373,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670874</v>
+        <v>127670907</v>
       </c>
       <c r="B9" t="n">
-        <v>78787</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,24 +1403,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1430,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449564</v>
+        <v>449605</v>
       </c>
       <c r="R9" t="n">
-        <v>6720313</v>
+        <v>6720348</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1493,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670574</v>
+        <v>127670874</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,31 +1508,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1536,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449419</v>
+        <v>449564</v>
       </c>
       <c r="R10" t="n">
-        <v>6720156</v>
+        <v>6720313</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1580,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R11" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R12" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127671236</v>
+        <v>127670838</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449454</v>
+        <v>449579</v>
       </c>
       <c r="R16" t="n">
-        <v>6720176</v>
+        <v>6720260</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670513</v>
+        <v>127671236</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449366</v>
+        <v>449454</v>
       </c>
       <c r="R17" t="n">
-        <v>6720133</v>
+        <v>6720176</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,11 +2283,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670838</v>
+        <v>127670513</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2326,21 +2321,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2353,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449579</v>
+        <v>449366</v>
       </c>
       <c r="R18" t="n">
-        <v>6720260</v>
+        <v>6720133</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2389,6 +2384,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,42 +2416,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670094</v>
+        <v>127670496</v>
       </c>
       <c r="B19" t="n">
-        <v>56864</v>
+        <v>78788</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449196</v>
+        <v>449359</v>
       </c>
       <c r="R19" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,6 +2498,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2517,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670771</v>
+        <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449600</v>
+        <v>449363</v>
       </c>
       <c r="R20" t="n">
-        <v>6720158</v>
+        <v>6720137</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2622,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670000</v>
+        <v>127670771</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2660,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449159</v>
+        <v>449600</v>
       </c>
       <c r="R21" t="n">
-        <v>6720222</v>
+        <v>6720158</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2723,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670476</v>
+        <v>127670000</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,21 +2730,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2761,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449363</v>
+        <v>449159</v>
       </c>
       <c r="R22" t="n">
-        <v>6720137</v>
+        <v>6720222</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2824,37 +2820,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670496</v>
+        <v>127670094</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2862,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449359</v>
+        <v>449196</v>
       </c>
       <c r="R23" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2906,7 +2907,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670849</v>
+        <v>127670032</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449556</v>
+        <v>449165</v>
       </c>
       <c r="R24" t="n">
-        <v>6720283</v>
+        <v>6720228</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670032</v>
+        <v>127670299</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449165</v>
+        <v>449181</v>
       </c>
       <c r="R25" t="n">
-        <v>6720228</v>
+        <v>6720023</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670299</v>
+        <v>127670849</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449181</v>
+        <v>449556</v>
       </c>
       <c r="R26" t="n">
-        <v>6720023</v>
+        <v>6720283</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127671028</v>
+        <v>127670556</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449628</v>
+        <v>449417</v>
       </c>
       <c r="R31" t="n">
-        <v>6720374</v>
+        <v>6720161</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,6 +3706,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670556</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449417</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720161</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3807,11 +3812,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670762</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449570</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720155</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671216</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449453</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720203</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4142,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671229</v>
+        <v>127671216</v>
       </c>
       <c r="B36" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449442</v>
+        <v>449453</v>
       </c>
       <c r="R36" t="n">
-        <v>6720178</v>
+        <v>6720203</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4445,39 +4445,35 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127670266</v>
+        <v>127670702</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4487,10 +4483,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449176</v>
+        <v>449550</v>
       </c>
       <c r="R39" t="n">
-        <v>6720025</v>
+        <v>6720131</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4550,35 +4546,39 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127670702</v>
+        <v>127670266</v>
       </c>
       <c r="B40" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449550</v>
+        <v>449176</v>
       </c>
       <c r="R40" t="n">
-        <v>6720131</v>
+        <v>6720025</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671241</v>
+        <v>127670593</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449445</v>
+        <v>449457</v>
       </c>
       <c r="R41" t="n">
-        <v>6720188</v>
+        <v>6720089</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670364</v>
+        <v>127671241</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449245</v>
+        <v>449445</v>
       </c>
       <c r="R43" t="n">
-        <v>6720058</v>
+        <v>6720188</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670593</v>
+        <v>127670364</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449457</v>
+        <v>449245</v>
       </c>
       <c r="R44" t="n">
-        <v>6720089</v>
+        <v>6720058</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670889</v>
+        <v>127670722</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449605</v>
+        <v>449567</v>
       </c>
       <c r="R48" t="n">
-        <v>6720315</v>
+        <v>6720141</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670722</v>
+        <v>127670889</v>
       </c>
       <c r="B50" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449567</v>
+        <v>449605</v>
       </c>
       <c r="R50" t="n">
-        <v>6720141</v>
+        <v>6720315</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670788</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449583</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720169</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671194</v>
+        <v>127670649</v>
       </c>
       <c r="B52" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449456</v>
+        <v>449438</v>
       </c>
       <c r="R52" t="n">
-        <v>6720223</v>
+        <v>6720136</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670754</v>
+        <v>127671143</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449589</v>
+        <v>449435</v>
       </c>
       <c r="R53" t="n">
-        <v>6720140</v>
+        <v>6720323</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670921</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449580</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720362</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670649</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449438</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720136</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670788</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449583</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720169</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670921</v>
+        <v>127670754</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449580</v>
+        <v>449589</v>
       </c>
       <c r="R57" t="n">
-        <v>6720362</v>
+        <v>6720140</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670181</v>
+        <v>127671129</v>
       </c>
       <c r="B59" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449202</v>
+        <v>449427</v>
       </c>
       <c r="R59" t="n">
-        <v>6720148</v>
+        <v>6720322</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670743</v>
+        <v>127670181</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449576</v>
+        <v>449202</v>
       </c>
       <c r="R60" t="n">
-        <v>6720141</v>
+        <v>6720148</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671129</v>
+        <v>127670743</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449427</v>
+        <v>449576</v>
       </c>
       <c r="R62" t="n">
-        <v>6720322</v>
+        <v>6720141</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670731</v>
+        <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449569</v>
+        <v>449210</v>
       </c>
       <c r="R63" t="n">
-        <v>6720138</v>
+        <v>6720149</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6982,10 +6982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670152</v>
+        <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7020,10 +7020,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449210</v>
+        <v>449656</v>
       </c>
       <c r="R64" t="n">
-        <v>6720149</v>
+        <v>6720358</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127670981</v>
+        <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>79647</v>
+        <v>78788</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7094,21 +7094,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449656</v>
+        <v>449569</v>
       </c>
       <c r="R65" t="n">
-        <v>6720358</v>
+        <v>6720138</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670605</v>
+        <v>127669907</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449451</v>
+        <v>449153</v>
       </c>
       <c r="R66" t="n">
-        <v>6720105</v>
+        <v>6720237</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670953</v>
+        <v>127670605</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449638</v>
+        <v>449451</v>
       </c>
       <c r="R67" t="n">
-        <v>6720356</v>
+        <v>6720105</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127669907</v>
+        <v>127670953</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449153</v>
+        <v>449638</v>
       </c>
       <c r="R69" t="n">
-        <v>6720237</v>
+        <v>6720356</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670324</v>
+        <v>127670200</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449217</v>
+        <v>449202</v>
       </c>
       <c r="R70" t="n">
-        <v>6720024</v>
+        <v>6720096</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670200</v>
+        <v>127670485</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7705,21 +7705,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449202</v>
+        <v>449358</v>
       </c>
       <c r="R71" t="n">
-        <v>6720096</v>
+        <v>6720139</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670485</v>
+        <v>127670324</v>
       </c>
       <c r="B73" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7907,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449358</v>
+        <v>449217</v>
       </c>
       <c r="R73" t="n">
-        <v>6720139</v>
+        <v>6720024</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -7997,10 +7997,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670710</v>
+        <v>127670054</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>91372</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,24 +8008,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8035,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449560</v>
+        <v>449185</v>
       </c>
       <c r="R74" t="n">
-        <v>6720133</v>
+        <v>6720192</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8098,10 +8102,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670054</v>
+        <v>127670272</v>
       </c>
       <c r="B75" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8109,28 +8113,24 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449185</v>
+        <v>449168</v>
       </c>
       <c r="R75" t="n">
-        <v>6720192</v>
+        <v>6720012</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670272</v>
+        <v>127670710</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449168</v>
+        <v>449560</v>
       </c>
       <c r="R77" t="n">
-        <v>6720012</v>
+        <v>6720133</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R11" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R12" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670556</v>
+        <v>127670762</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449417</v>
+        <v>449570</v>
       </c>
       <c r="R31" t="n">
-        <v>6720161</v>
+        <v>6720155</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,11 +3706,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3738,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127670556</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3744,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449417</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720161</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3812,6 +3807,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -5661,37 +5661,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>56864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5699,10 +5708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5743,7 +5752,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670649</v>
+        <v>127671194</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5808,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449438</v>
+        <v>449456</v>
       </c>
       <c r="R52" t="n">
-        <v>6720136</v>
+        <v>6720223</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5871,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671143</v>
+        <v>127670649</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5901,10 +5909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449435</v>
+        <v>449438</v>
       </c>
       <c r="R53" t="n">
-        <v>6720323</v>
+        <v>6720136</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670921</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6002,10 +6010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449580</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720362</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6073,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670921</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6103,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449580</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720362</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6174,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670788</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6204,10 +6212,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449583</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720169</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,7 +6275,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670754</v>
+        <v>127670788</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449589</v>
+        <v>449583</v>
       </c>
       <c r="R57" t="n">
-        <v>6720140</v>
+        <v>6720169</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127670754</v>
       </c>
       <c r="B58" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449589</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720140</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671129</v>
+        <v>127670781</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449427</v>
+        <v>449586</v>
       </c>
       <c r="R59" t="n">
-        <v>6720322</v>
+        <v>6720154</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670181</v>
+        <v>127670743</v>
       </c>
       <c r="B60" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449202</v>
+        <v>449576</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720141</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670781</v>
+        <v>127670181</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449586</v>
+        <v>449202</v>
       </c>
       <c r="R61" t="n">
-        <v>6720154</v>
+        <v>6720148</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670743</v>
+        <v>127671129</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449576</v>
+        <v>449427</v>
       </c>
       <c r="R62" t="n">
-        <v>6720141</v>
+        <v>6720322</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R11" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R12" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670762</v>
+        <v>127670556</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449570</v>
+        <v>449417</v>
       </c>
       <c r="R31" t="n">
-        <v>6720155</v>
+        <v>6720161</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,6 +3706,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670556</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449417</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720161</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3807,11 +3812,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -5661,46 +5661,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669856</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>56864</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5708,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449125</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720233</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5752,6 +5743,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671194</v>
+        <v>127670649</v>
       </c>
       <c r="B52" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5808,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449456</v>
+        <v>449438</v>
       </c>
       <c r="R52" t="n">
-        <v>6720223</v>
+        <v>6720136</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5871,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5909,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R53" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670921</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6010,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449580</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720362</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670921</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6111,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449580</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720362</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670788</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6212,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449583</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720169</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,7 +6267,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670788</v>
+        <v>127670754</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6313,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449583</v>
+        <v>449589</v>
       </c>
       <c r="R57" t="n">
-        <v>6720169</v>
+        <v>6720140</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670754</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449589</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720140</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127670445</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>78788</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449296</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720275</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670445</v>
+        <v>127671216</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449296</v>
+        <v>449453</v>
       </c>
       <c r="R37" t="n">
-        <v>6720275</v>
+        <v>6720203</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671175</v>
+        <v>127670907</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,24 +888,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -915,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449421</v>
+        <v>449605</v>
       </c>
       <c r="R4" t="n">
-        <v>6720306</v>
+        <v>6720348</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127670874</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449564</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720313</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670618</v>
+        <v>127671175</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1117,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449457</v>
+        <v>449421</v>
       </c>
       <c r="R6" t="n">
-        <v>6720117</v>
+        <v>6720306</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,43 +1184,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671018</v>
+        <v>127671038</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449633</v>
+        <v>449628</v>
       </c>
       <c r="R7" t="n">
-        <v>6720378</v>
+        <v>6720382</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670574</v>
+        <v>127670618</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,31 +1296,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1330,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449419</v>
+        <v>449457</v>
       </c>
       <c r="R8" t="n">
-        <v>6720156</v>
+        <v>6720117</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1374,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670907</v>
+        <v>127670574</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,30 +1397,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449605</v>
+        <v>449419</v>
       </c>
       <c r="R9" t="n">
-        <v>6720348</v>
+        <v>6720156</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1478,7 +1473,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1497,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670874</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>78787</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449564</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720313</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670556</v>
+        <v>127670762</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449417</v>
+        <v>449570</v>
       </c>
       <c r="R31" t="n">
-        <v>6720161</v>
+        <v>6720155</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,11 +3706,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3738,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127670556</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3744,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449417</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720161</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3812,6 +3807,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670445</v>
+        <v>127671229</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>91352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449296</v>
+        <v>449442</v>
       </c>
       <c r="R34" t="n">
-        <v>6720275</v>
+        <v>6720178</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671229</v>
+        <v>127670934</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449442</v>
+        <v>449622</v>
       </c>
       <c r="R35" t="n">
-        <v>6720178</v>
+        <v>6720346</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127671216</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449453</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720203</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127671216</v>
+        <v>127670445</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449453</v>
+        <v>449296</v>
       </c>
       <c r="R37" t="n">
-        <v>6720203</v>
+        <v>6720275</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -5661,37 +5661,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127669856</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>56864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5699,10 +5708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449125</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720233</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5743,7 +5752,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5762,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670649</v>
+        <v>127671194</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5773,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5800,10 +5808,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449438</v>
+        <v>449456</v>
       </c>
       <c r="R52" t="n">
-        <v>6720136</v>
+        <v>6720223</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5863,7 +5871,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671143</v>
+        <v>127670649</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5901,10 +5909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449435</v>
+        <v>449438</v>
       </c>
       <c r="R53" t="n">
-        <v>6720323</v>
+        <v>6720136</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670921</v>
+        <v>127671143</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6002,10 +6010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449580</v>
+        <v>449435</v>
       </c>
       <c r="R54" t="n">
-        <v>6720362</v>
+        <v>6720323</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,7 +6073,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127670921</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6103,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449580</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720362</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6174,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670788</v>
+        <v>127670280</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6204,10 +6212,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449583</v>
+        <v>449176</v>
       </c>
       <c r="R56" t="n">
-        <v>6720169</v>
+        <v>6720013</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,7 +6275,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670754</v>
+        <v>127670788</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449589</v>
+        <v>449583</v>
       </c>
       <c r="R57" t="n">
-        <v>6720140</v>
+        <v>6720169</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127670754</v>
       </c>
       <c r="B58" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449589</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720140</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127669907</v>
+        <v>127670605</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449153</v>
+        <v>449451</v>
       </c>
       <c r="R66" t="n">
-        <v>6720237</v>
+        <v>6720105</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670605</v>
+        <v>127670541</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449451</v>
+        <v>449410</v>
       </c>
       <c r="R67" t="n">
-        <v>6720105</v>
+        <v>6720148</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,6 +7359,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7386,10 +7391,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670541</v>
+        <v>127670953</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7397,21 +7402,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7424,10 +7429,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449410</v>
+        <v>449638</v>
       </c>
       <c r="R68" t="n">
-        <v>6720148</v>
+        <v>6720356</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7460,11 +7465,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670953</v>
+        <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449638</v>
+        <v>449153</v>
       </c>
       <c r="R69" t="n">
-        <v>6720356</v>
+        <v>6720237</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127671028</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449628</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720374</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670762</v>
+        <v>127670556</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449570</v>
+        <v>449417</v>
       </c>
       <c r="R31" t="n">
-        <v>6720155</v>
+        <v>6720161</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,6 +3706,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3733,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670556</v>
+        <v>127670762</v>
       </c>
       <c r="B32" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,21 +3749,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449417</v>
+        <v>449570</v>
       </c>
       <c r="R32" t="n">
-        <v>6720161</v>
+        <v>6720155</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3807,11 +3812,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R33" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127671229</v>
+        <v>127670445</v>
       </c>
       <c r="B34" t="n">
-        <v>91352</v>
+        <v>78788</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449442</v>
+        <v>449296</v>
       </c>
       <c r="R34" t="n">
-        <v>6720178</v>
+        <v>6720275</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670934</v>
+        <v>127671229</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4052,21 +4052,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449622</v>
+        <v>449442</v>
       </c>
       <c r="R35" t="n">
-        <v>6720346</v>
+        <v>6720178</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R36" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670445</v>
+        <v>127671216</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449296</v>
+        <v>449453</v>
       </c>
       <c r="R37" t="n">
-        <v>6720275</v>
+        <v>6720203</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -5661,46 +5661,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127669856</v>
+        <v>127671194</v>
       </c>
       <c r="B51" t="n">
-        <v>56864</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5708,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449125</v>
+        <v>449456</v>
       </c>
       <c r="R51" t="n">
-        <v>6720233</v>
+        <v>6720223</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5752,6 +5743,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5762,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671194</v>
+        <v>127670649</v>
       </c>
       <c r="B52" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5773,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5808,10 +5800,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449456</v>
+        <v>449438</v>
       </c>
       <c r="R52" t="n">
-        <v>6720223</v>
+        <v>6720136</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5871,7 +5863,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670649</v>
+        <v>127671143</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5909,10 +5901,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449438</v>
+        <v>449435</v>
       </c>
       <c r="R53" t="n">
-        <v>6720136</v>
+        <v>6720323</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671143</v>
+        <v>127670921</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -6010,10 +6002,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449435</v>
+        <v>449580</v>
       </c>
       <c r="R54" t="n">
-        <v>6720323</v>
+        <v>6720362</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,7 +6065,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670921</v>
+        <v>127670280</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6111,10 +6103,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449580</v>
+        <v>449176</v>
       </c>
       <c r="R55" t="n">
-        <v>6720362</v>
+        <v>6720013</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,7 +6166,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670280</v>
+        <v>127670788</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -6212,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449176</v>
+        <v>449583</v>
       </c>
       <c r="R56" t="n">
-        <v>6720013</v>
+        <v>6720169</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,7 +6267,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670788</v>
+        <v>127670754</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6313,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449583</v>
+        <v>449589</v>
       </c>
       <c r="R57" t="n">
-        <v>6720169</v>
+        <v>6720140</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6376,37 +6368,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670754</v>
+        <v>127669856</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6414,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449589</v>
+        <v>449125</v>
       </c>
       <c r="R58" t="n">
-        <v>6720140</v>
+        <v>6720233</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6458,7 +6459,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670605</v>
+        <v>127669907</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449451</v>
+        <v>449153</v>
       </c>
       <c r="R66" t="n">
-        <v>6720105</v>
+        <v>6720237</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670541</v>
+        <v>127670605</v>
       </c>
       <c r="B67" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449410</v>
+        <v>449451</v>
       </c>
       <c r="R67" t="n">
-        <v>6720148</v>
+        <v>6720105</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7359,11 +7359,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7391,10 +7386,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670953</v>
+        <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7402,21 +7397,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7429,10 +7424,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449638</v>
+        <v>449410</v>
       </c>
       <c r="R68" t="n">
-        <v>6720356</v>
+        <v>6720148</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7465,6 +7460,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127669907</v>
+        <v>127670953</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449153</v>
+        <v>449638</v>
       </c>
       <c r="R69" t="n">
-        <v>6720237</v>
+        <v>6720356</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670907</v>
+        <v>127671175</v>
       </c>
       <c r="B4" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,28 +888,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -919,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449605</v>
+        <v>449421</v>
       </c>
       <c r="R4" t="n">
-        <v>6720348</v>
+        <v>6720306</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670874</v>
+        <v>127671038</v>
       </c>
       <c r="B5" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449564</v>
+        <v>449628</v>
       </c>
       <c r="R5" t="n">
-        <v>6720313</v>
+        <v>6720382</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127671175</v>
+        <v>127670618</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1121,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449421</v>
+        <v>449457</v>
       </c>
       <c r="R6" t="n">
-        <v>6720306</v>
+        <v>6720117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1184,37 +1180,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671038</v>
+        <v>127671018</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1222,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449628</v>
+        <v>449633</v>
       </c>
       <c r="R7" t="n">
-        <v>6720382</v>
+        <v>6720378</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1285,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670618</v>
+        <v>127670574</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,26 +1298,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1323,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449457</v>
+        <v>449419</v>
       </c>
       <c r="R8" t="n">
-        <v>6720117</v>
+        <v>6720156</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1367,7 +1374,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670574</v>
+        <v>127670907</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>91372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,31 +1403,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449419</v>
+        <v>449605</v>
       </c>
       <c r="R9" t="n">
-        <v>6720156</v>
+        <v>6720348</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1473,6 +1478,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,43 +1497,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670874</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449564</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720313</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670781</v>
+        <v>127671129</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449586</v>
+        <v>449427</v>
       </c>
       <c r="R59" t="n">
-        <v>6720154</v>
+        <v>6720322</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670743</v>
+        <v>127670181</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449576</v>
+        <v>449202</v>
       </c>
       <c r="R60" t="n">
-        <v>6720141</v>
+        <v>6720148</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670181</v>
+        <v>127670781</v>
       </c>
       <c r="B61" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449202</v>
+        <v>449586</v>
       </c>
       <c r="R61" t="n">
-        <v>6720148</v>
+        <v>6720154</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671129</v>
+        <v>127670743</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6791,21 +6791,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449427</v>
+        <v>449576</v>
       </c>
       <c r="R62" t="n">
-        <v>6720322</v>
+        <v>6720141</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127671164</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127670008</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671175</v>
+        <v>127671038</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R4" t="n">
-        <v>6720306</v>
+        <v>6720382</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127671038</v>
+        <v>127670907</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>91380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,24 +989,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1016,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R5" t="n">
-        <v>6720382</v>
+        <v>6720348</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1079,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670618</v>
+        <v>127670574</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,26 +1094,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1117,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449457</v>
+        <v>449419</v>
       </c>
       <c r="R6" t="n">
-        <v>6720117</v>
+        <v>6720156</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1161,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,43 +1188,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671018</v>
+        <v>127671175</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449633</v>
+        <v>449421</v>
       </c>
       <c r="R7" t="n">
-        <v>6720378</v>
+        <v>6720306</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1287,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670574</v>
+        <v>127670874</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>78790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,31 +1300,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1330,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449419</v>
+        <v>449564</v>
       </c>
       <c r="R8" t="n">
-        <v>6720156</v>
+        <v>6720313</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1374,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670907</v>
+        <v>127670618</v>
       </c>
       <c r="B9" t="n">
-        <v>91372</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,28 +1401,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1434,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449605</v>
+        <v>449457</v>
       </c>
       <c r="R9" t="n">
-        <v>6720348</v>
+        <v>6720117</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1497,37 +1491,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670874</v>
+        <v>127671018</v>
       </c>
       <c r="B10" t="n">
-        <v>78787</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449564</v>
+        <v>449633</v>
       </c>
       <c r="R10" t="n">
-        <v>6720313</v>
+        <v>6720378</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127671259</v>
+        <v>127670319</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449417</v>
+        <v>449199</v>
       </c>
       <c r="R11" t="n">
-        <v>6720181</v>
+        <v>6720015</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670319</v>
+        <v>127671259</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449199</v>
+        <v>449417</v>
       </c>
       <c r="R12" t="n">
-        <v>6720015</v>
+        <v>6720181</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1803,7 +1803,7 @@
         <v>127670132</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>127671204</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>127671090</v>
       </c>
       <c r="B15" t="n">
-        <v>98390</v>
+        <v>98398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670838</v>
+        <v>127671236</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449579</v>
+        <v>449454</v>
       </c>
       <c r="R16" t="n">
-        <v>6720260</v>
+        <v>6720176</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127671236</v>
+        <v>127670513</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449454</v>
+        <v>449366</v>
       </c>
       <c r="R17" t="n">
-        <v>6720176</v>
+        <v>6720133</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,6 +2283,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670513</v>
+        <v>127670838</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>78790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2321,21 +2326,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449366</v>
+        <v>449579</v>
       </c>
       <c r="R18" t="n">
-        <v>6720133</v>
+        <v>6720260</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2384,11 +2389,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,10 +2416,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670496</v>
+        <v>127670771</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449359</v>
+        <v>449600</v>
       </c>
       <c r="R19" t="n">
-        <v>6720133</v>
+        <v>6720158</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2520,7 +2520,7 @@
         <v>127670476</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670771</v>
+        <v>127670000</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449600</v>
+        <v>449159</v>
       </c>
       <c r="R21" t="n">
-        <v>6720158</v>
+        <v>6720222</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2719,37 +2719,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670000</v>
+        <v>127670094</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2757,10 +2762,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449159</v>
+        <v>449196</v>
       </c>
       <c r="R22" t="n">
-        <v>6720222</v>
+        <v>6720173</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2801,7 +2806,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,42 +2824,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670094</v>
+        <v>127670496</v>
       </c>
       <c r="B23" t="n">
-        <v>56864</v>
+        <v>78791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2863,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449196</v>
+        <v>449359</v>
       </c>
       <c r="R23" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2907,6 +2906,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670032</v>
+        <v>127670118</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449165</v>
+        <v>449175</v>
       </c>
       <c r="R24" t="n">
-        <v>6720228</v>
+        <v>6720175</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670299</v>
+        <v>127670849</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449181</v>
+        <v>449556</v>
       </c>
       <c r="R25" t="n">
-        <v>6720023</v>
+        <v>6720283</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670849</v>
+        <v>127670032</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449556</v>
+        <v>449165</v>
       </c>
       <c r="R26" t="n">
-        <v>6720283</v>
+        <v>6720228</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670118</v>
+        <v>127670299</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,21 +3239,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449175</v>
+        <v>449181</v>
       </c>
       <c r="R27" t="n">
-        <v>6720175</v>
+        <v>6720023</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127671028</v>
+        <v>127669984</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449628</v>
+        <v>449175</v>
       </c>
       <c r="R28" t="n">
-        <v>6720374</v>
+        <v>6720229</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3433,7 +3433,7 @@
         <v>127671155</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>127670217</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3632,10 +3632,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670556</v>
+        <v>127671028</v>
       </c>
       <c r="B31" t="n">
-        <v>80132</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,21 +3643,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449417</v>
+        <v>449628</v>
       </c>
       <c r="R31" t="n">
-        <v>6720161</v>
+        <v>6720374</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3706,11 +3706,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3738,10 +3733,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670762</v>
+        <v>127670556</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>80135</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,21 +3744,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449570</v>
+        <v>449417</v>
       </c>
       <c r="R32" t="n">
-        <v>6720155</v>
+        <v>6720161</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3812,6 +3807,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127669984</v>
+        <v>127670762</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449175</v>
+        <v>449570</v>
       </c>
       <c r="R33" t="n">
-        <v>6720229</v>
+        <v>6720155</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3943,7 +3943,7 @@
         <v>127670445</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>127671229</v>
       </c>
       <c r="B35" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>127670934</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>127671216</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>127670341</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4445,35 +4445,39 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127670702</v>
+        <v>127670266</v>
       </c>
       <c r="B39" t="n">
-        <v>79647</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4483,10 +4487,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449550</v>
+        <v>449176</v>
       </c>
       <c r="R39" t="n">
-        <v>6720131</v>
+        <v>6720025</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4546,39 +4550,35 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127670266</v>
+        <v>127670702</v>
       </c>
       <c r="B40" t="n">
-        <v>92642</v>
+        <v>79650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449176</v>
+        <v>449550</v>
       </c>
       <c r="R40" t="n">
-        <v>6720025</v>
+        <v>6720131</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127670593</v>
+        <v>127671241</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449457</v>
+        <v>449445</v>
       </c>
       <c r="R41" t="n">
-        <v>6720089</v>
+        <v>6720188</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670625</v>
+        <v>127670593</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449440</v>
+        <v>449457</v>
       </c>
       <c r="R42" t="n">
-        <v>6720118</v>
+        <v>6720089</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671241</v>
+        <v>127670625</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449445</v>
+        <v>449440</v>
       </c>
       <c r="R43" t="n">
-        <v>6720188</v>
+        <v>6720118</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4957,7 +4957,7 @@
         <v>127670364</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>127670309</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>127670448</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>127670335</v>
       </c>
       <c r="B47" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670722</v>
+        <v>127670168</v>
       </c>
       <c r="B48" t="n">
-        <v>79647</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5369,21 +5369,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449567</v>
+        <v>449195</v>
       </c>
       <c r="R48" t="n">
-        <v>6720141</v>
+        <v>6720146</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670168</v>
+        <v>127670889</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449195</v>
+        <v>449605</v>
       </c>
       <c r="R49" t="n">
-        <v>6720146</v>
+        <v>6720315</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,10 +5560,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670889</v>
+        <v>127670722</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79650</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449605</v>
+        <v>449567</v>
       </c>
       <c r="R50" t="n">
-        <v>6720315</v>
+        <v>6720141</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671194</v>
+        <v>127670754</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5672,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449456</v>
+        <v>449589</v>
       </c>
       <c r="R51" t="n">
-        <v>6720223</v>
+        <v>6720140</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,37 +5762,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670649</v>
+        <v>127669856</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5800,10 +5809,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449438</v>
+        <v>449125</v>
       </c>
       <c r="R52" t="n">
-        <v>6720136</v>
+        <v>6720233</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5844,7 +5853,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5863,10 +5871,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671143</v>
+        <v>127671194</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>91360</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5874,21 +5882,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5901,10 +5909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449435</v>
+        <v>449456</v>
       </c>
       <c r="R53" t="n">
-        <v>6720323</v>
+        <v>6720223</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5964,10 +5972,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670921</v>
+        <v>127670788</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6002,10 +6010,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449580</v>
+        <v>449583</v>
       </c>
       <c r="R54" t="n">
-        <v>6720362</v>
+        <v>6720169</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6065,10 +6073,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670280</v>
+        <v>127671143</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6103,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449176</v>
+        <v>449435</v>
       </c>
       <c r="R55" t="n">
-        <v>6720013</v>
+        <v>6720323</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,10 +6174,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670788</v>
+        <v>127670649</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,10 +6212,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449583</v>
+        <v>449438</v>
       </c>
       <c r="R56" t="n">
-        <v>6720169</v>
+        <v>6720136</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,10 +6275,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670754</v>
+        <v>127670280</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449589</v>
+        <v>449176</v>
       </c>
       <c r="R57" t="n">
-        <v>6720140</v>
+        <v>6720013</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6368,46 +6376,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127669856</v>
+        <v>127670921</v>
       </c>
       <c r="B58" t="n">
-        <v>56864</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6415,10 +6414,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449125</v>
+        <v>449580</v>
       </c>
       <c r="R58" t="n">
-        <v>6720233</v>
+        <v>6720362</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6459,6 +6458,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671129</v>
+        <v>127670181</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>78790</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6488,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6515,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449427</v>
+        <v>449202</v>
       </c>
       <c r="R59" t="n">
-        <v>6720322</v>
+        <v>6720148</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6578,10 +6578,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670181</v>
+        <v>127670781</v>
       </c>
       <c r="B60" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6589,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449202</v>
+        <v>449586</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720154</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670781</v>
+        <v>127671129</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449586</v>
+        <v>449427</v>
       </c>
       <c r="R61" t="n">
-        <v>6720154</v>
+        <v>6720322</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6783,7 +6783,7 @@
         <v>127670743</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>127670152</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>127670981</v>
       </c>
       <c r="B64" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>127670731</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7184,10 +7184,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127669907</v>
+        <v>127670953</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,21 +7195,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449153</v>
+        <v>449638</v>
       </c>
       <c r="R66" t="n">
-        <v>6720237</v>
+        <v>6720356</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7288,7 +7288,7 @@
         <v>127670605</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>127670541</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670953</v>
+        <v>127669907</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,21 +7503,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7530,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449638</v>
+        <v>449153</v>
       </c>
       <c r="R69" t="n">
-        <v>6720356</v>
+        <v>6720237</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7593,10 +7593,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670200</v>
+        <v>127670324</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449202</v>
+        <v>449217</v>
       </c>
       <c r="R70" t="n">
-        <v>6720096</v>
+        <v>6720024</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,10 +7694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670485</v>
+        <v>127670200</v>
       </c>
       <c r="B71" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7705,21 +7705,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449358</v>
+        <v>449202</v>
       </c>
       <c r="R71" t="n">
-        <v>6720139</v>
+        <v>6720096</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,10 +7795,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670825</v>
+        <v>127670485</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449573</v>
+        <v>449358</v>
       </c>
       <c r="R72" t="n">
-        <v>6720260</v>
+        <v>6720139</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670324</v>
+        <v>127670825</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449217</v>
+        <v>449573</v>
       </c>
       <c r="R73" t="n">
-        <v>6720024</v>
+        <v>6720260</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8000,7 +8000,7 @@
         <v>127670054</v>
       </c>
       <c r="B74" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670272</v>
+        <v>127670710</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449168</v>
+        <v>449560</v>
       </c>
       <c r="R75" t="n">
-        <v>6720012</v>
+        <v>6720133</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8206,7 +8206,7 @@
         <v>127671250</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670710</v>
+        <v>127670272</v>
       </c>
       <c r="B77" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449560</v>
+        <v>449168</v>
       </c>
       <c r="R77" t="n">
-        <v>6720133</v>
+        <v>6720012</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127671164</v>
+        <v>127671194</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449428</v>
+        <v>449456</v>
       </c>
       <c r="R2" t="n">
-        <v>6720312</v>
+        <v>6720223</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127670008</v>
+        <v>127671229</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449167</v>
+        <v>449442</v>
       </c>
       <c r="R3" t="n">
-        <v>6720240</v>
+        <v>6720178</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127671038</v>
+        <v>127670266</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,24 +888,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -915,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449628</v>
+        <v>449176</v>
       </c>
       <c r="R4" t="n">
-        <v>6720382</v>
+        <v>6720025</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670907</v>
+        <v>127670054</v>
       </c>
       <c r="B5" t="n">
-        <v>91380</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,7 +1012,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1020,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449605</v>
+        <v>449185</v>
       </c>
       <c r="R5" t="n">
-        <v>6720348</v>
+        <v>6720192</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670574</v>
+        <v>127670335</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,31 +1098,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1126,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449419</v>
+        <v>449221</v>
       </c>
       <c r="R6" t="n">
-        <v>6720156</v>
+        <v>6720036</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1170,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127671175</v>
+        <v>127670907</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,24 +1199,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1226,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449421</v>
+        <v>449605</v>
       </c>
       <c r="R7" t="n">
-        <v>6720306</v>
+        <v>6720348</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1289,32 +1293,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670874</v>
+        <v>127670000</v>
       </c>
       <c r="B8" t="n">
-        <v>78790</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449564</v>
+        <v>449159</v>
       </c>
       <c r="R8" t="n">
-        <v>6720313</v>
+        <v>6720222</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1390,14 +1394,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670618</v>
+        <v>127670008</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1428,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449457</v>
+        <v>449167</v>
       </c>
       <c r="R9" t="n">
-        <v>6720117</v>
+        <v>6720240</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1491,43 +1495,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127671018</v>
+        <v>127670032</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1535,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449633</v>
+        <v>449165</v>
       </c>
       <c r="R10" t="n">
-        <v>6720378</v>
+        <v>6720228</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1598,32 +1596,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670319</v>
+        <v>127670132</v>
       </c>
       <c r="B11" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449199</v>
+        <v>449194</v>
       </c>
       <c r="R11" t="n">
-        <v>6720015</v>
+        <v>6720159</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1699,14 +1697,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127671259</v>
+        <v>127670152</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1737,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449417</v>
+        <v>449210</v>
       </c>
       <c r="R12" t="n">
-        <v>6720181</v>
+        <v>6720149</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1800,14 +1798,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127670132</v>
+        <v>127670168</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1838,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449194</v>
+        <v>449195</v>
       </c>
       <c r="R13" t="n">
-        <v>6720159</v>
+        <v>6720146</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1901,14 +1899,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127671204</v>
+        <v>127670200</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1939,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449443</v>
+        <v>449202</v>
       </c>
       <c r="R14" t="n">
-        <v>6720234</v>
+        <v>6720096</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2002,42 +2000,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127671090</v>
+        <v>127670217</v>
       </c>
       <c r="B15" t="n">
-        <v>98398</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2045,10 +2038,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449480</v>
+        <v>449200</v>
       </c>
       <c r="R15" t="n">
-        <v>6720296</v>
+        <v>6720125</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2108,14 +2101,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127671236</v>
+        <v>127670272</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2146,10 +2139,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449454</v>
+        <v>449168</v>
       </c>
       <c r="R16" t="n">
-        <v>6720176</v>
+        <v>6720012</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2209,32 +2202,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670513</v>
+        <v>127670280</v>
       </c>
       <c r="B17" t="n">
-        <v>80135</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449366</v>
+        <v>449176</v>
       </c>
       <c r="R17" t="n">
-        <v>6720133</v>
+        <v>6720013</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2283,11 +2276,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2315,32 +2303,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670838</v>
+        <v>127670299</v>
       </c>
       <c r="B18" t="n">
-        <v>78790</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2353,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449579</v>
+        <v>449181</v>
       </c>
       <c r="R18" t="n">
-        <v>6720260</v>
+        <v>6720023</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2416,14 +2404,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670771</v>
+        <v>127670324</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2454,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449600</v>
+        <v>449217</v>
       </c>
       <c r="R19" t="n">
-        <v>6720158</v>
+        <v>6720024</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2517,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670476</v>
+        <v>127670341</v>
       </c>
       <c r="B20" t="n">
-        <v>79650</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449363</v>
+        <v>449227</v>
       </c>
       <c r="R20" t="n">
-        <v>6720137</v>
+        <v>6720046</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2618,14 +2606,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670000</v>
+        <v>127670364</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2656,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449159</v>
+        <v>449245</v>
       </c>
       <c r="R21" t="n">
-        <v>6720222</v>
+        <v>6720058</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2719,42 +2707,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670094</v>
+        <v>127670593</v>
       </c>
       <c r="B22" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2762,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449196</v>
+        <v>449457</v>
       </c>
       <c r="R22" t="n">
-        <v>6720173</v>
+        <v>6720089</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2806,6 +2789,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,32 +2808,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670496</v>
+        <v>127670605</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449359</v>
+        <v>449451</v>
       </c>
       <c r="R23" t="n">
-        <v>6720133</v>
+        <v>6720105</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2925,32 +2909,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670118</v>
+        <v>127670618</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449175</v>
+        <v>449457</v>
       </c>
       <c r="R24" t="n">
-        <v>6720175</v>
+        <v>6720117</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3026,14 +3010,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670849</v>
+        <v>127670625</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3064,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449556</v>
+        <v>449440</v>
       </c>
       <c r="R25" t="n">
-        <v>6720283</v>
+        <v>6720118</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3127,14 +3111,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670032</v>
+        <v>127670649</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3165,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449165</v>
+        <v>449438</v>
       </c>
       <c r="R26" t="n">
-        <v>6720228</v>
+        <v>6720136</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3228,14 +3212,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670299</v>
+        <v>127670743</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3266,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449181</v>
+        <v>449576</v>
       </c>
       <c r="R27" t="n">
-        <v>6720023</v>
+        <v>6720141</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3329,32 +3313,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127669984</v>
+        <v>127670754</v>
       </c>
       <c r="B28" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449175</v>
+        <v>449589</v>
       </c>
       <c r="R28" t="n">
-        <v>6720229</v>
+        <v>6720140</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3430,14 +3414,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127671155</v>
+        <v>127670762</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3468,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449421</v>
+        <v>449570</v>
       </c>
       <c r="R29" t="n">
-        <v>6720319</v>
+        <v>6720155</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3531,14 +3515,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670217</v>
+        <v>127670771</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3569,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449200</v>
+        <v>449600</v>
       </c>
       <c r="R30" t="n">
-        <v>6720125</v>
+        <v>6720158</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3632,14 +3616,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127671028</v>
+        <v>127670781</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3670,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449628</v>
+        <v>449586</v>
       </c>
       <c r="R31" t="n">
-        <v>6720374</v>
+        <v>6720154</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3733,32 +3717,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670556</v>
+        <v>127670788</v>
       </c>
       <c r="B32" t="n">
-        <v>80135</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449417</v>
+        <v>449583</v>
       </c>
       <c r="R32" t="n">
-        <v>6720161</v>
+        <v>6720169</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3807,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,14 +3818,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670762</v>
+        <v>127670825</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3877,10 +3856,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449570</v>
+        <v>449573</v>
       </c>
       <c r="R33" t="n">
-        <v>6720155</v>
+        <v>6720260</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3940,32 +3919,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670445</v>
+        <v>127670849</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3978,10 +3957,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449296</v>
+        <v>449556</v>
       </c>
       <c r="R34" t="n">
-        <v>6720275</v>
+        <v>6720283</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4041,32 +4020,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127671229</v>
+        <v>127670889</v>
       </c>
       <c r="B35" t="n">
-        <v>91360</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4079,10 +4058,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449442</v>
+        <v>449605</v>
       </c>
       <c r="R35" t="n">
-        <v>6720178</v>
+        <v>6720315</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4142,14 +4121,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670934</v>
+        <v>127670921</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4180,10 +4159,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449622</v>
+        <v>449580</v>
       </c>
       <c r="R36" t="n">
-        <v>6720346</v>
+        <v>6720362</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4243,14 +4222,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127671216</v>
+        <v>127670934</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4281,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449453</v>
+        <v>449622</v>
       </c>
       <c r="R37" t="n">
-        <v>6720203</v>
+        <v>6720346</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4344,14 +4323,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127670341</v>
+        <v>127670953</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4382,10 +4361,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449227</v>
+        <v>449638</v>
       </c>
       <c r="R38" t="n">
-        <v>6720046</v>
+        <v>6720356</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4445,39 +4424,35 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127670266</v>
+        <v>127671028</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4487,10 +4462,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449176</v>
+        <v>449628</v>
       </c>
       <c r="R39" t="n">
-        <v>6720025</v>
+        <v>6720374</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4550,32 +4525,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127670702</v>
+        <v>127671038</v>
       </c>
       <c r="B40" t="n">
-        <v>79650</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4588,10 +4563,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449550</v>
+        <v>449628</v>
       </c>
       <c r="R40" t="n">
-        <v>6720131</v>
+        <v>6720382</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4651,14 +4626,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671241</v>
+        <v>127671143</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4689,10 +4664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449445</v>
+        <v>449435</v>
       </c>
       <c r="R41" t="n">
-        <v>6720188</v>
+        <v>6720323</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4752,14 +4727,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127670593</v>
+        <v>127671155</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4790,10 +4765,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449457</v>
+        <v>449421</v>
       </c>
       <c r="R42" t="n">
-        <v>6720089</v>
+        <v>6720319</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4853,14 +4828,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127670625</v>
+        <v>127671164</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4891,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449440</v>
+        <v>449428</v>
       </c>
       <c r="R43" t="n">
-        <v>6720118</v>
+        <v>6720312</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4954,14 +4929,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127670364</v>
+        <v>127671175</v>
       </c>
       <c r="B44" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4992,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449245</v>
+        <v>449421</v>
       </c>
       <c r="R44" t="n">
-        <v>6720058</v>
+        <v>6720306</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5055,32 +5030,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127670309</v>
+        <v>127671204</v>
       </c>
       <c r="B45" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5068,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449202</v>
+        <v>449443</v>
       </c>
       <c r="R45" t="n">
-        <v>6720026</v>
+        <v>6720234</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5156,32 +5131,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127670448</v>
+        <v>127671216</v>
       </c>
       <c r="B46" t="n">
-        <v>78791</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449292</v>
+        <v>449453</v>
       </c>
       <c r="R46" t="n">
-        <v>6720271</v>
+        <v>6720203</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5257,32 +5232,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127670335</v>
+        <v>127671236</v>
       </c>
       <c r="B47" t="n">
-        <v>91380</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5295,10 +5270,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>449221</v>
+        <v>449454</v>
       </c>
       <c r="R47" t="n">
-        <v>6720036</v>
+        <v>6720176</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5358,14 +5333,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127670168</v>
+        <v>127671241</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5396,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449195</v>
+        <v>449445</v>
       </c>
       <c r="R48" t="n">
-        <v>6720146</v>
+        <v>6720188</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5459,14 +5434,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127670889</v>
+        <v>127671250</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5497,10 +5472,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449605</v>
+        <v>449429</v>
       </c>
       <c r="R49" t="n">
-        <v>6720315</v>
+        <v>6720186</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5560,32 +5535,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127670722</v>
+        <v>127671259</v>
       </c>
       <c r="B50" t="n">
-        <v>79650</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5573,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449567</v>
+        <v>449417</v>
       </c>
       <c r="R50" t="n">
-        <v>6720141</v>
+        <v>6720181</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5661,10 +5636,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670754</v>
+        <v>127670181</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5672,21 +5647,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5674,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449589</v>
+        <v>449202</v>
       </c>
       <c r="R51" t="n">
-        <v>6720140</v>
+        <v>6720148</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5762,46 +5737,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127669856</v>
+        <v>127670485</v>
       </c>
       <c r="B52" t="n">
-        <v>56864</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5809,10 +5775,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449125</v>
+        <v>449358</v>
       </c>
       <c r="R52" t="n">
-        <v>6720233</v>
+        <v>6720139</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5853,6 +5819,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5871,10 +5838,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671194</v>
+        <v>127670838</v>
       </c>
       <c r="B53" t="n">
-        <v>91360</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,21 +5849,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5909,10 +5876,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449456</v>
+        <v>449579</v>
       </c>
       <c r="R53" t="n">
-        <v>6720223</v>
+        <v>6720260</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5972,10 +5939,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670788</v>
+        <v>127670874</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5983,21 +5950,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6010,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449583</v>
+        <v>449564</v>
       </c>
       <c r="R54" t="n">
-        <v>6720169</v>
+        <v>6720313</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6073,10 +6040,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671143</v>
+        <v>127670476</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,21 +6051,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6078,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449435</v>
+        <v>449363</v>
       </c>
       <c r="R55" t="n">
-        <v>6720323</v>
+        <v>6720137</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6174,10 +6141,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670649</v>
+        <v>127670702</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6185,21 +6152,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6212,10 +6179,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449438</v>
+        <v>449550</v>
       </c>
       <c r="R56" t="n">
-        <v>6720136</v>
+        <v>6720131</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6275,10 +6242,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670280</v>
+        <v>127670722</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6286,21 +6253,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6313,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449176</v>
+        <v>449567</v>
       </c>
       <c r="R57" t="n">
-        <v>6720013</v>
+        <v>6720141</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6376,10 +6343,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670921</v>
+        <v>127670981</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6387,21 +6354,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6414,10 +6381,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449580</v>
+        <v>449656</v>
       </c>
       <c r="R58" t="n">
-        <v>6720362</v>
+        <v>6720358</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6477,10 +6444,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670181</v>
+        <v>127670513</v>
       </c>
       <c r="B59" t="n">
-        <v>78790</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,21 +6455,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6515,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449202</v>
+        <v>449366</v>
       </c>
       <c r="R59" t="n">
-        <v>6720148</v>
+        <v>6720133</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6551,6 +6518,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6578,10 +6550,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670781</v>
+        <v>127670541</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6589,21 +6561,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6616,10 +6588,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449586</v>
+        <v>449410</v>
       </c>
       <c r="R60" t="n">
-        <v>6720154</v>
+        <v>6720148</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6652,6 +6624,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6679,10 +6656,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671129</v>
+        <v>127670556</v>
       </c>
       <c r="B61" t="n">
-        <v>78791</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6690,21 +6667,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6717,10 +6694,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449427</v>
+        <v>449417</v>
       </c>
       <c r="R61" t="n">
-        <v>6720322</v>
+        <v>6720161</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6753,6 +6730,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6780,37 +6762,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670743</v>
+        <v>127670574</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6818,10 +6805,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449576</v>
+        <v>449419</v>
       </c>
       <c r="R62" t="n">
-        <v>6720141</v>
+        <v>6720156</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6862,7 +6849,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6881,37 +6867,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127670152</v>
+        <v>127669856</v>
       </c>
       <c r="B63" t="n">
-        <v>79032</v>
+        <v>57141</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6919,10 +6914,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449210</v>
+        <v>449125</v>
       </c>
       <c r="R63" t="n">
-        <v>6720149</v>
+        <v>6720233</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6963,7 +6958,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6982,37 +6976,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670981</v>
+        <v>127670094</v>
       </c>
       <c r="B64" t="n">
-        <v>79650</v>
+        <v>57141</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7020,10 +7019,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449656</v>
+        <v>449196</v>
       </c>
       <c r="R64" t="n">
-        <v>6720358</v>
+        <v>6720173</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7064,7 +7063,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7083,37 +7081,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127670731</v>
+        <v>127671018</v>
       </c>
       <c r="B65" t="n">
-        <v>78791</v>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7121,10 +7125,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449569</v>
+        <v>449633</v>
       </c>
       <c r="R65" t="n">
-        <v>6720138</v>
+        <v>6720378</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7184,37 +7188,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127670953</v>
+        <v>127671090</v>
       </c>
       <c r="B66" t="n">
-        <v>79032</v>
+        <v>99038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7222,10 +7231,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449638</v>
+        <v>449480</v>
       </c>
       <c r="R66" t="n">
-        <v>6720356</v>
+        <v>6720296</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7285,10 +7294,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127670605</v>
+        <v>127669907</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,21 +7305,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7323,10 +7332,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449451</v>
+        <v>449153</v>
       </c>
       <c r="R67" t="n">
-        <v>6720105</v>
+        <v>6720237</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7386,10 +7395,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127670541</v>
+        <v>127669984</v>
       </c>
       <c r="B68" t="n">
-        <v>80135</v>
+        <v>79085</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7397,21 +7406,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7424,10 +7433,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449410</v>
+        <v>449175</v>
       </c>
       <c r="R68" t="n">
-        <v>6720148</v>
+        <v>6720229</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7460,11 +7469,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7492,10 +7496,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127669907</v>
+        <v>127670118</v>
       </c>
       <c r="B69" t="n">
-        <v>78791</v>
+        <v>79085</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7530,10 +7534,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449153</v>
+        <v>449175</v>
       </c>
       <c r="R69" t="n">
-        <v>6720237</v>
+        <v>6720175</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7593,10 +7597,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670324</v>
+        <v>127670309</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7604,21 +7608,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449217</v>
+        <v>449202</v>
       </c>
       <c r="R70" t="n">
-        <v>6720024</v>
+        <v>6720026</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7694,10 +7698,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670200</v>
+        <v>127670319</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7705,21 +7709,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7732,10 +7736,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449202</v>
+        <v>449199</v>
       </c>
       <c r="R71" t="n">
-        <v>6720096</v>
+        <v>6720015</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7795,10 +7799,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670485</v>
+        <v>127670445</v>
       </c>
       <c r="B72" t="n">
-        <v>78790</v>
+        <v>79085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7806,21 +7810,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7833,10 +7837,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449358</v>
+        <v>449296</v>
       </c>
       <c r="R72" t="n">
-        <v>6720139</v>
+        <v>6720275</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7896,10 +7900,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670825</v>
+        <v>127670448</v>
       </c>
       <c r="B73" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7907,21 +7911,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7934,10 +7938,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449573</v>
+        <v>449292</v>
       </c>
       <c r="R73" t="n">
-        <v>6720260</v>
+        <v>6720271</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -7997,10 +8001,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670054</v>
+        <v>127670496</v>
       </c>
       <c r="B74" t="n">
-        <v>91380</v>
+        <v>79085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,28 +8012,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449185</v>
+        <v>449359</v>
       </c>
       <c r="R74" t="n">
-        <v>6720192</v>
+        <v>6720133</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8105,7 +8105,7 @@
         <v>127670710</v>
       </c>
       <c r="B75" t="n">
-        <v>78791</v>
+        <v>79085</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127671250</v>
+        <v>127670731</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8214,21 +8214,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449429</v>
+        <v>449569</v>
       </c>
       <c r="R76" t="n">
-        <v>6720186</v>
+        <v>6720138</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127670272</v>
+        <v>127671129</v>
       </c>
       <c r="B77" t="n">
-        <v>79032</v>
+        <v>79085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8315,21 +8315,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449168</v>
+        <v>449427</v>
       </c>
       <c r="R77" t="n">
-        <v>6720012</v>
+        <v>6720322</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127671194</v>
+        <v>135406923</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449456</v>
+        <v>449069</v>
       </c>
       <c r="R2" t="n">
-        <v>6720223</v>
+        <v>6720040</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -743,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,37 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127671229</v>
+        <v>135406928</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449442</v>
+        <v>449081</v>
       </c>
       <c r="R3" t="n">
-        <v>6720178</v>
+        <v>6720036</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -844,12 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,41 +885,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670266</v>
+        <v>135406980</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449176</v>
+        <v>449081</v>
       </c>
       <c r="R4" t="n">
-        <v>6720025</v>
+        <v>6720030</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -949,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,7 +972,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670054</v>
+        <v>127671194</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,28 +1001,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1024,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449185</v>
+        <v>449456</v>
       </c>
       <c r="R5" t="n">
-        <v>6720192</v>
+        <v>6720223</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670335</v>
+        <v>127671229</v>
       </c>
       <c r="B6" t="n">
-        <v>91930</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449221</v>
+        <v>449442</v>
       </c>
       <c r="R6" t="n">
-        <v>6720036</v>
+        <v>6720178</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1188,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670907</v>
+        <v>127670266</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,26 +1203,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1230,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449605</v>
+        <v>449176</v>
       </c>
       <c r="R7" t="n">
-        <v>6720348</v>
+        <v>6720025</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1293,35 +1297,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670000</v>
+        <v>127670054</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1331,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449159</v>
+        <v>449185</v>
       </c>
       <c r="R8" t="n">
-        <v>6720222</v>
+        <v>6720192</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1394,32 +1402,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670008</v>
+        <v>127670335</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449167</v>
+        <v>449221</v>
       </c>
       <c r="R9" t="n">
-        <v>6720240</v>
+        <v>6720036</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1495,35 +1503,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670032</v>
+        <v>127670907</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1533,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449165</v>
+        <v>449605</v>
       </c>
       <c r="R10" t="n">
-        <v>6720228</v>
+        <v>6720348</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1596,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670132</v>
+        <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>91995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449194</v>
+        <v>449228</v>
       </c>
       <c r="R11" t="n">
-        <v>6720159</v>
+        <v>6720113</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1664,12 +1676,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1697,32 +1709,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670152</v>
+        <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>91995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449210</v>
+        <v>449244</v>
       </c>
       <c r="R12" t="n">
-        <v>6720149</v>
+        <v>6720123</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1765,12 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127670168</v>
+        <v>127670000</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1836,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449195</v>
+        <v>449159</v>
       </c>
       <c r="R13" t="n">
-        <v>6720146</v>
+        <v>6720222</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1899,7 +1911,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127670200</v>
+        <v>127670008</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1937,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449202</v>
+        <v>449167</v>
       </c>
       <c r="R14" t="n">
-        <v>6720096</v>
+        <v>6720240</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2000,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670217</v>
+        <v>127670032</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2038,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449200</v>
+        <v>449165</v>
       </c>
       <c r="R15" t="n">
-        <v>6720125</v>
+        <v>6720228</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2101,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670272</v>
+        <v>127670132</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2139,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449168</v>
+        <v>449194</v>
       </c>
       <c r="R16" t="n">
-        <v>6720012</v>
+        <v>6720159</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2202,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670280</v>
+        <v>127670152</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2240,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449176</v>
+        <v>449210</v>
       </c>
       <c r="R17" t="n">
-        <v>6720013</v>
+        <v>6720149</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2303,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670299</v>
+        <v>127670168</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2341,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449181</v>
+        <v>449195</v>
       </c>
       <c r="R18" t="n">
-        <v>6720023</v>
+        <v>6720146</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2404,7 +2416,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670324</v>
+        <v>127670200</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2442,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449217</v>
+        <v>449202</v>
       </c>
       <c r="R19" t="n">
-        <v>6720024</v>
+        <v>6720096</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2505,7 +2517,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670341</v>
+        <v>127670217</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2543,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449227</v>
+        <v>449200</v>
       </c>
       <c r="R20" t="n">
-        <v>6720046</v>
+        <v>6720125</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2606,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670364</v>
+        <v>127670272</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2644,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449245</v>
+        <v>449168</v>
       </c>
       <c r="R21" t="n">
-        <v>6720058</v>
+        <v>6720012</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2707,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670593</v>
+        <v>127670280</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2745,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449457</v>
+        <v>449176</v>
       </c>
       <c r="R22" t="n">
-        <v>6720089</v>
+        <v>6720013</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2808,7 +2820,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670605</v>
+        <v>127670299</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2846,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449451</v>
+        <v>449181</v>
       </c>
       <c r="R23" t="n">
-        <v>6720105</v>
+        <v>6720023</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2909,7 +2921,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670618</v>
+        <v>127670324</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -2947,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449457</v>
+        <v>449217</v>
       </c>
       <c r="R24" t="n">
-        <v>6720117</v>
+        <v>6720024</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3010,7 +3022,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670625</v>
+        <v>127670341</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3048,10 +3060,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449440</v>
+        <v>449227</v>
       </c>
       <c r="R25" t="n">
-        <v>6720118</v>
+        <v>6720046</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3111,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670649</v>
+        <v>127670364</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3149,10 +3161,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449438</v>
+        <v>449245</v>
       </c>
       <c r="R26" t="n">
-        <v>6720136</v>
+        <v>6720058</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3212,7 +3224,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670743</v>
+        <v>127670593</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3250,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449576</v>
+        <v>449457</v>
       </c>
       <c r="R27" t="n">
-        <v>6720141</v>
+        <v>6720089</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3313,7 +3325,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127670754</v>
+        <v>127670605</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3351,10 +3363,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449589</v>
+        <v>449451</v>
       </c>
       <c r="R28" t="n">
-        <v>6720140</v>
+        <v>6720105</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3414,7 +3426,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127670762</v>
+        <v>127670618</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3452,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449570</v>
+        <v>449457</v>
       </c>
       <c r="R29" t="n">
-        <v>6720155</v>
+        <v>6720117</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3515,7 +3527,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670771</v>
+        <v>127670625</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3553,10 +3565,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449600</v>
+        <v>449440</v>
       </c>
       <c r="R30" t="n">
-        <v>6720158</v>
+        <v>6720118</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3616,7 +3628,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670781</v>
+        <v>127670649</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3654,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449586</v>
+        <v>449438</v>
       </c>
       <c r="R31" t="n">
-        <v>6720154</v>
+        <v>6720136</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3717,7 +3729,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670788</v>
+        <v>127670743</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3755,10 +3767,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449583</v>
+        <v>449576</v>
       </c>
       <c r="R32" t="n">
-        <v>6720169</v>
+        <v>6720141</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3818,7 +3830,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670825</v>
+        <v>127670754</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3856,10 +3868,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449573</v>
+        <v>449589</v>
       </c>
       <c r="R33" t="n">
-        <v>6720260</v>
+        <v>6720140</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -3919,7 +3931,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670849</v>
+        <v>127670762</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -3957,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449556</v>
+        <v>449570</v>
       </c>
       <c r="R34" t="n">
-        <v>6720283</v>
+        <v>6720155</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4020,7 +4032,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670889</v>
+        <v>127670771</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4058,10 +4070,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449605</v>
+        <v>449600</v>
       </c>
       <c r="R35" t="n">
-        <v>6720315</v>
+        <v>6720158</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4121,7 +4133,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670921</v>
+        <v>127670781</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4159,10 +4171,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449580</v>
+        <v>449586</v>
       </c>
       <c r="R36" t="n">
-        <v>6720362</v>
+        <v>6720154</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4222,7 +4234,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670934</v>
+        <v>127670788</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4260,10 +4272,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449622</v>
+        <v>449583</v>
       </c>
       <c r="R37" t="n">
-        <v>6720346</v>
+        <v>6720169</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4323,7 +4335,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127670953</v>
+        <v>127670825</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4361,10 +4373,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449638</v>
+        <v>449573</v>
       </c>
       <c r="R38" t="n">
-        <v>6720356</v>
+        <v>6720260</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4424,7 +4436,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671028</v>
+        <v>127670849</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4462,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449628</v>
+        <v>449556</v>
       </c>
       <c r="R39" t="n">
-        <v>6720374</v>
+        <v>6720283</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4525,7 +4537,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671038</v>
+        <v>127670889</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4563,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R40" t="n">
-        <v>6720382</v>
+        <v>6720315</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4626,7 +4638,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671143</v>
+        <v>127670921</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -4664,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449435</v>
+        <v>449580</v>
       </c>
       <c r="R41" t="n">
-        <v>6720323</v>
+        <v>6720362</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4727,7 +4739,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127671155</v>
+        <v>127670934</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -4765,10 +4777,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449421</v>
+        <v>449622</v>
       </c>
       <c r="R42" t="n">
-        <v>6720319</v>
+        <v>6720346</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -4828,7 +4840,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671164</v>
+        <v>127670953</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -4866,10 +4878,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449428</v>
+        <v>449638</v>
       </c>
       <c r="R43" t="n">
-        <v>6720312</v>
+        <v>6720356</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -4929,7 +4941,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671175</v>
+        <v>127671028</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -4967,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R44" t="n">
-        <v>6720306</v>
+        <v>6720374</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5030,7 +5042,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671204</v>
+        <v>127671038</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5068,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449443</v>
+        <v>449628</v>
       </c>
       <c r="R45" t="n">
-        <v>6720234</v>
+        <v>6720382</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5131,7 +5143,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671216</v>
+        <v>127671143</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5169,10 +5181,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449453</v>
+        <v>449435</v>
       </c>
       <c r="R46" t="n">
-        <v>6720203</v>
+        <v>6720323</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5232,7 +5244,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671236</v>
+        <v>127671155</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5270,10 +5282,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>449454</v>
+        <v>449421</v>
       </c>
       <c r="R47" t="n">
-        <v>6720176</v>
+        <v>6720319</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5333,7 +5345,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671241</v>
+        <v>127671164</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5371,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449445</v>
+        <v>449428</v>
       </c>
       <c r="R48" t="n">
-        <v>6720188</v>
+        <v>6720312</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5434,7 +5446,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671250</v>
+        <v>127671175</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5472,10 +5484,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449429</v>
+        <v>449421</v>
       </c>
       <c r="R49" t="n">
-        <v>6720186</v>
+        <v>6720306</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5535,7 +5547,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671259</v>
+        <v>127671204</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5573,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449417</v>
+        <v>449443</v>
       </c>
       <c r="R50" t="n">
-        <v>6720181</v>
+        <v>6720234</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5636,32 +5648,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670181</v>
+        <v>127671216</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5674,10 +5686,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449202</v>
+        <v>449453</v>
       </c>
       <c r="R51" t="n">
-        <v>6720148</v>
+        <v>6720203</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5737,32 +5749,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670485</v>
+        <v>127671236</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5775,10 +5787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449358</v>
+        <v>449454</v>
       </c>
       <c r="R52" t="n">
-        <v>6720139</v>
+        <v>6720176</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -5838,32 +5850,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670838</v>
+        <v>127671241</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5876,10 +5888,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449579</v>
+        <v>449445</v>
       </c>
       <c r="R53" t="n">
-        <v>6720260</v>
+        <v>6720188</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5939,32 +5951,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670874</v>
+        <v>127671250</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5977,10 +5989,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449564</v>
+        <v>449429</v>
       </c>
       <c r="R54" t="n">
-        <v>6720313</v>
+        <v>6720186</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6040,32 +6052,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670476</v>
+        <v>127671259</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6078,10 +6090,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449363</v>
+        <v>449417</v>
       </c>
       <c r="R55" t="n">
-        <v>6720137</v>
+        <v>6720181</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6141,10 +6153,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670702</v>
+        <v>127670181</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6152,21 +6164,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6179,10 +6191,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449550</v>
+        <v>449202</v>
       </c>
       <c r="R56" t="n">
-        <v>6720131</v>
+        <v>6720148</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6242,10 +6254,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670722</v>
+        <v>127670485</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6253,21 +6265,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6280,10 +6292,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449567</v>
+        <v>449358</v>
       </c>
       <c r="R57" t="n">
-        <v>6720141</v>
+        <v>6720139</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6343,10 +6355,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670981</v>
+        <v>127670838</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6354,21 +6366,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6381,10 +6393,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449656</v>
+        <v>449579</v>
       </c>
       <c r="R58" t="n">
-        <v>6720358</v>
+        <v>6720260</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6444,10 +6456,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670513</v>
+        <v>127670874</v>
       </c>
       <c r="B59" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6455,21 +6467,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6482,10 +6494,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449366</v>
+        <v>449564</v>
       </c>
       <c r="R59" t="n">
-        <v>6720133</v>
+        <v>6720313</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6518,11 +6530,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6550,10 +6557,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670541</v>
+        <v>127670476</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6561,21 +6568,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6588,10 +6595,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449410</v>
+        <v>449363</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720137</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6624,11 +6631,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6656,10 +6658,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670556</v>
+        <v>127670702</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6667,21 +6669,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6694,10 +6696,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449417</v>
+        <v>449550</v>
       </c>
       <c r="R61" t="n">
-        <v>6720161</v>
+        <v>6720131</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -6730,11 +6732,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6762,42 +6759,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670574</v>
+        <v>127670722</v>
       </c>
       <c r="B62" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6805,10 +6797,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449419</v>
+        <v>449567</v>
       </c>
       <c r="R62" t="n">
-        <v>6720156</v>
+        <v>6720141</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -6849,6 +6841,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6867,46 +6860,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127669856</v>
+        <v>127670981</v>
       </c>
       <c r="B63" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6914,10 +6898,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449125</v>
+        <v>449656</v>
       </c>
       <c r="R63" t="n">
-        <v>6720233</v>
+        <v>6720358</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -6958,6 +6942,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6976,42 +6961,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670094</v>
+        <v>127670513</v>
       </c>
       <c r="B64" t="n">
-        <v>57141</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7019,10 +6999,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449196</v>
+        <v>449366</v>
       </c>
       <c r="R64" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7057,12 +7037,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7081,43 +7067,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671018</v>
+        <v>127670541</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7125,10 +7105,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449633</v>
+        <v>449410</v>
       </c>
       <c r="R65" t="n">
-        <v>6720378</v>
+        <v>6720148</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7161,6 +7141,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7188,42 +7173,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127671090</v>
+        <v>127670556</v>
       </c>
       <c r="B66" t="n">
-        <v>99038</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7231,10 +7211,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449480</v>
+        <v>449417</v>
       </c>
       <c r="R66" t="n">
-        <v>6720296</v>
+        <v>6720161</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7267,6 +7247,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7294,37 +7279,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127669907</v>
+        <v>127670574</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7332,10 +7322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449153</v>
+        <v>449419</v>
       </c>
       <c r="R67" t="n">
-        <v>6720237</v>
+        <v>6720156</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7376,7 +7366,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7395,10 +7384,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127669984</v>
+        <v>135407060</v>
       </c>
       <c r="B68" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7406,26 +7395,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7433,10 +7427,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449175</v>
+        <v>449236</v>
       </c>
       <c r="R68" t="n">
-        <v>6720229</v>
+        <v>6720036</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7463,12 +7457,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7477,7 +7476,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7496,10 +7494,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670118</v>
+        <v>135407083</v>
       </c>
       <c r="B69" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7507,26 +7505,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7534,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449175</v>
+        <v>449247</v>
       </c>
       <c r="R69" t="n">
-        <v>6720175</v>
+        <v>6720048</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7564,12 +7567,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7578,7 +7586,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7597,10 +7604,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670309</v>
+        <v>135407098</v>
       </c>
       <c r="B70" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7608,26 +7615,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7635,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449202</v>
+        <v>449230</v>
       </c>
       <c r="R70" t="n">
-        <v>6720026</v>
+        <v>6720102</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -7665,12 +7677,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7679,7 +7696,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7698,10 +7714,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670319</v>
+        <v>135407111</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7709,26 +7725,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7736,10 +7757,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449199</v>
+        <v>449176</v>
       </c>
       <c r="R71" t="n">
-        <v>6720015</v>
+        <v>6720201</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -7766,12 +7787,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7780,7 +7806,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7799,10 +7824,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670445</v>
+        <v>135407127</v>
       </c>
       <c r="B72" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7810,26 +7835,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7837,10 +7867,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449296</v>
+        <v>449187</v>
       </c>
       <c r="R72" t="n">
-        <v>6720275</v>
+        <v>6720212</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -7867,12 +7897,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7881,7 +7916,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7900,10 +7934,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670448</v>
+        <v>135407137</v>
       </c>
       <c r="B73" t="n">
-        <v>79085</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7911,26 +7945,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7938,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449292</v>
+        <v>449192</v>
       </c>
       <c r="R73" t="n">
-        <v>6720271</v>
+        <v>6720196</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -7968,12 +8007,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7982,7 +8026,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8001,37 +8044,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670496</v>
+        <v>127669856</v>
       </c>
       <c r="B74" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8039,10 +8091,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449359</v>
+        <v>449125</v>
       </c>
       <c r="R74" t="n">
-        <v>6720133</v>
+        <v>6720233</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8083,7 +8135,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8102,37 +8153,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670710</v>
+        <v>127670094</v>
       </c>
       <c r="B75" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8140,10 +8196,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449560</v>
+        <v>449196</v>
       </c>
       <c r="R75" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8184,7 +8240,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8203,37 +8258,42 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670731</v>
+        <v>135405777</v>
       </c>
       <c r="B76" t="n">
-        <v>79085</v>
+        <v>57162</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8241,10 +8301,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449569</v>
+        <v>449287</v>
       </c>
       <c r="R76" t="n">
-        <v>6720138</v>
+        <v>6720229</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8271,12 +8331,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8285,7 +8345,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8304,37 +8363,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127671129</v>
+        <v>135407156</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>57162</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8342,10 +8406,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449427</v>
+        <v>449198</v>
       </c>
       <c r="R77" t="n">
-        <v>6720322</v>
+        <v>6720054</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8372,12 +8436,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8386,7 +8450,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8402,6 +8465,1960 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135407169</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>449231</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6720053</v>
+      </c>
+      <c r="S78" t="n">
+        <v>50</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135407185</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>449169</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6720150</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135407195</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>449157</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6720238</v>
+      </c>
+      <c r="S80" t="n">
+        <v>50</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135407205</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>449174</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6720215</v>
+      </c>
+      <c r="S81" t="n">
+        <v>50</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135407225</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>449185</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6720200</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135407236</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>449494</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S83" t="n">
+        <v>50</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127671018</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>449633</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6720378</v>
+      </c>
+      <c r="S84" t="n">
+        <v>50</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127671090</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>449480</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6720296</v>
+      </c>
+      <c r="S85" t="n">
+        <v>50</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127669907</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>449153</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6720237</v>
+      </c>
+      <c r="S86" t="n">
+        <v>50</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127669984</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>449175</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6720229</v>
+      </c>
+      <c r="S87" t="n">
+        <v>50</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127670118</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>449175</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6720175</v>
+      </c>
+      <c r="S88" t="n">
+        <v>50</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127670309</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>449202</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6720026</v>
+      </c>
+      <c r="S89" t="n">
+        <v>50</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127670319</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>449199</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6720015</v>
+      </c>
+      <c r="S90" t="n">
+        <v>50</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127670445</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>449296</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6720275</v>
+      </c>
+      <c r="S91" t="n">
+        <v>50</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127670448</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>449292</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6720271</v>
+      </c>
+      <c r="S92" t="n">
+        <v>50</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127670496</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>449359</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S93" t="n">
+        <v>50</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127670710</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>449560</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S94" t="n">
+        <v>50</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127670731</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>449569</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6720138</v>
+      </c>
+      <c r="S95" t="n">
+        <v>50</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127671129</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>449427</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6720322</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9098,10 +9098,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127671018</v>
+        <v>135448394</v>
       </c>
       <c r="B84" t="n">
-        <v>8455</v>
+        <v>57162</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9109,30 +9109,29 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9142,13 +9141,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>449633</v>
+        <v>449299</v>
       </c>
       <c r="R84" t="n">
-        <v>6720378</v>
+        <v>6720032</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9172,12 +9171,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färsk spillning på sten</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9186,29 +9200,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127671090</v>
+        <v>135448816</v>
       </c>
       <c r="B85" t="n">
-        <v>99038</v>
+        <v>57162</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9216,31 +9229,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9248,13 +9261,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>449480</v>
+        <v>449149</v>
       </c>
       <c r="R85" t="n">
-        <v>6720296</v>
+        <v>6720071</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9278,12 +9291,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Tjäderspillning på låg sten</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9292,56 +9320,60 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127669907</v>
+        <v>135448842</v>
       </c>
       <c r="B86" t="n">
-        <v>79085</v>
+        <v>57162</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9349,13 +9381,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>449153</v>
+        <v>449177</v>
       </c>
       <c r="R86" t="n">
-        <v>6720237</v>
+        <v>6720087</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9379,12 +9411,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>på sten</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9393,56 +9440,60 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127669984</v>
+        <v>135448854</v>
       </c>
       <c r="B87" t="n">
-        <v>79085</v>
+        <v>57162</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9450,13 +9501,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>449175</v>
+        <v>449141</v>
       </c>
       <c r="R87" t="n">
-        <v>6720229</v>
+        <v>6720065</v>
       </c>
       <c r="S87" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9480,12 +9531,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9494,56 +9560,61 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127670118</v>
+        <v>127671018</v>
       </c>
       <c r="B88" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9551,10 +9622,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>449175</v>
+        <v>449633</v>
       </c>
       <c r="R88" t="n">
-        <v>6720175</v>
+        <v>6720378</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -9614,37 +9685,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127670309</v>
+        <v>127671090</v>
       </c>
       <c r="B89" t="n">
-        <v>79085</v>
+        <v>99038</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>223597</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9652,10 +9728,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>449202</v>
+        <v>449480</v>
       </c>
       <c r="R89" t="n">
-        <v>6720026</v>
+        <v>6720296</v>
       </c>
       <c r="S89" t="n">
         <v>50</v>
@@ -9715,7 +9791,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127670319</v>
+        <v>127669907</v>
       </c>
       <c r="B90" t="n">
         <v>79085</v>
@@ -9753,10 +9829,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>449199</v>
+        <v>449153</v>
       </c>
       <c r="R90" t="n">
-        <v>6720015</v>
+        <v>6720237</v>
       </c>
       <c r="S90" t="n">
         <v>50</v>
@@ -9816,7 +9892,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127670445</v>
+        <v>127669984</v>
       </c>
       <c r="B91" t="n">
         <v>79085</v>
@@ -9854,10 +9930,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>449296</v>
+        <v>449175</v>
       </c>
       <c r="R91" t="n">
-        <v>6720275</v>
+        <v>6720229</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -9917,7 +9993,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127670448</v>
+        <v>127670118</v>
       </c>
       <c r="B92" t="n">
         <v>79085</v>
@@ -9955,10 +10031,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>449292</v>
+        <v>449175</v>
       </c>
       <c r="R92" t="n">
-        <v>6720271</v>
+        <v>6720175</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10018,7 +10094,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127670496</v>
+        <v>127670309</v>
       </c>
       <c r="B93" t="n">
         <v>79085</v>
@@ -10056,10 +10132,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>449359</v>
+        <v>449202</v>
       </c>
       <c r="R93" t="n">
-        <v>6720133</v>
+        <v>6720026</v>
       </c>
       <c r="S93" t="n">
         <v>50</v>
@@ -10119,7 +10195,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127670710</v>
+        <v>127670319</v>
       </c>
       <c r="B94" t="n">
         <v>79085</v>
@@ -10157,10 +10233,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>449560</v>
+        <v>449199</v>
       </c>
       <c r="R94" t="n">
-        <v>6720133</v>
+        <v>6720015</v>
       </c>
       <c r="S94" t="n">
         <v>50</v>
@@ -10220,7 +10296,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127670731</v>
+        <v>127670445</v>
       </c>
       <c r="B95" t="n">
         <v>79085</v>
@@ -10258,10 +10334,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>449569</v>
+        <v>449296</v>
       </c>
       <c r="R95" t="n">
-        <v>6720138</v>
+        <v>6720275</v>
       </c>
       <c r="S95" t="n">
         <v>50</v>
@@ -10321,7 +10397,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127671129</v>
+        <v>127670448</v>
       </c>
       <c r="B96" t="n">
         <v>79085</v>
@@ -10359,10 +10435,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>449427</v>
+        <v>449292</v>
       </c>
       <c r="R96" t="n">
-        <v>6720322</v>
+        <v>6720271</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10419,6 +10495,410 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127670496</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>449359</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S97" t="n">
+        <v>50</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127670710</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>449560</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S98" t="n">
+        <v>50</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127670731</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>449569</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6720138</v>
+      </c>
+      <c r="S99" t="n">
+        <v>50</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127671129</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>449427</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6720322</v>
+      </c>
+      <c r="S100" t="n">
+        <v>50</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9578,10 +9578,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127671018</v>
+        <v>135448981</v>
       </c>
       <c r="B88" t="n">
-        <v>8455</v>
+        <v>57162</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9589,30 +9589,29 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -9622,13 +9621,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>449633</v>
+        <v>449090</v>
       </c>
       <c r="R88" t="n">
-        <v>6720378</v>
+        <v>6720042</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9652,12 +9651,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>på sten</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9666,29 +9680,28 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127671090</v>
+        <v>135448995</v>
       </c>
       <c r="B89" t="n">
-        <v>99038</v>
+        <v>57162</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9696,31 +9709,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9728,13 +9741,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>449480</v>
+        <v>449098</v>
       </c>
       <c r="R89" t="n">
-        <v>6720296</v>
+        <v>6720041</v>
       </c>
       <c r="S89" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9758,12 +9771,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>på sten</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9772,56 +9800,61 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127669907</v>
+        <v>127671018</v>
       </c>
       <c r="B90" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9829,10 +9862,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>449153</v>
+        <v>449633</v>
       </c>
       <c r="R90" t="n">
-        <v>6720237</v>
+        <v>6720378</v>
       </c>
       <c r="S90" t="n">
         <v>50</v>
@@ -9892,37 +9925,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127669984</v>
+        <v>127671090</v>
       </c>
       <c r="B91" t="n">
-        <v>79085</v>
+        <v>99038</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>223597</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -9930,10 +9968,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>449175</v>
+        <v>449480</v>
       </c>
       <c r="R91" t="n">
-        <v>6720229</v>
+        <v>6720296</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -9993,7 +10031,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127670118</v>
+        <v>127669907</v>
       </c>
       <c r="B92" t="n">
         <v>79085</v>
@@ -10031,10 +10069,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>449175</v>
+        <v>449153</v>
       </c>
       <c r="R92" t="n">
-        <v>6720175</v>
+        <v>6720237</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10094,7 +10132,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127670309</v>
+        <v>127669984</v>
       </c>
       <c r="B93" t="n">
         <v>79085</v>
@@ -10132,10 +10170,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>449202</v>
+        <v>449175</v>
       </c>
       <c r="R93" t="n">
-        <v>6720026</v>
+        <v>6720229</v>
       </c>
       <c r="S93" t="n">
         <v>50</v>
@@ -10195,7 +10233,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127670319</v>
+        <v>127670118</v>
       </c>
       <c r="B94" t="n">
         <v>79085</v>
@@ -10233,10 +10271,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>449199</v>
+        <v>449175</v>
       </c>
       <c r="R94" t="n">
-        <v>6720015</v>
+        <v>6720175</v>
       </c>
       <c r="S94" t="n">
         <v>50</v>
@@ -10296,7 +10334,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127670445</v>
+        <v>127670309</v>
       </c>
       <c r="B95" t="n">
         <v>79085</v>
@@ -10334,10 +10372,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>449296</v>
+        <v>449202</v>
       </c>
       <c r="R95" t="n">
-        <v>6720275</v>
+        <v>6720026</v>
       </c>
       <c r="S95" t="n">
         <v>50</v>
@@ -10397,7 +10435,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127670448</v>
+        <v>127670319</v>
       </c>
       <c r="B96" t="n">
         <v>79085</v>
@@ -10435,10 +10473,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>449292</v>
+        <v>449199</v>
       </c>
       <c r="R96" t="n">
-        <v>6720271</v>
+        <v>6720015</v>
       </c>
       <c r="S96" t="n">
         <v>50</v>
@@ -10498,7 +10536,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127670496</v>
+        <v>127670445</v>
       </c>
       <c r="B97" t="n">
         <v>79085</v>
@@ -10536,10 +10574,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>449359</v>
+        <v>449296</v>
       </c>
       <c r="R97" t="n">
-        <v>6720133</v>
+        <v>6720275</v>
       </c>
       <c r="S97" t="n">
         <v>50</v>
@@ -10599,7 +10637,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127670710</v>
+        <v>127670448</v>
       </c>
       <c r="B98" t="n">
         <v>79085</v>
@@ -10637,10 +10675,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>449560</v>
+        <v>449292</v>
       </c>
       <c r="R98" t="n">
-        <v>6720133</v>
+        <v>6720271</v>
       </c>
       <c r="S98" t="n">
         <v>50</v>
@@ -10700,7 +10738,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127670731</v>
+        <v>127670496</v>
       </c>
       <c r="B99" t="n">
         <v>79085</v>
@@ -10738,10 +10776,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>449569</v>
+        <v>449359</v>
       </c>
       <c r="R99" t="n">
-        <v>6720138</v>
+        <v>6720133</v>
       </c>
       <c r="S99" t="n">
         <v>50</v>
@@ -10801,7 +10839,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127671129</v>
+        <v>127670710</v>
       </c>
       <c r="B100" t="n">
         <v>79085</v>
@@ -10839,10 +10877,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>449427</v>
+        <v>449560</v>
       </c>
       <c r="R100" t="n">
-        <v>6720322</v>
+        <v>6720133</v>
       </c>
       <c r="S100" t="n">
         <v>50</v>
@@ -10899,6 +10937,208 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127670731</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>449569</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6720138</v>
+      </c>
+      <c r="S101" t="n">
+        <v>50</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127671129</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>449427</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6720322</v>
+      </c>
+      <c r="S102" t="n">
+        <v>50</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406928</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671194</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670266</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670054</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670335</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670907</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407036</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670008</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670032</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670132</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2312,6 +2392,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670152</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670168</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2514,6 +2604,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670200</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670217</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2716,6 +2816,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670272</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670280</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2918,6 +3028,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670299</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3019,6 +3134,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670324</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670341</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670364</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3322,6 +3452,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670593</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3423,6 +3558,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670605</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3524,6 +3664,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670618</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3625,6 +3770,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670625</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3726,6 +3876,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670649</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3827,6 +3982,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670743</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3928,6 +4088,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670754</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4029,6 +4194,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670762</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4130,6 +4300,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670771</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4231,6 +4406,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670781</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4332,6 +4512,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670788</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4433,6 +4618,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670825</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4534,6 +4724,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670849</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4635,6 +4830,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670889</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4736,6 +4936,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670921</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4837,6 +5042,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670934</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4938,6 +5148,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670953</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5039,6 +5254,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671028</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5140,6 +5360,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671038</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5241,6 +5466,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671143</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5342,6 +5572,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671155</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5443,6 +5678,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671164</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5544,6 +5784,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671175</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5645,6 +5890,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671204</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5746,6 +5996,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671216</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5847,6 +6102,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671236</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5948,6 +6208,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671241</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6049,6 +6314,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671250</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6150,6 +6420,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671259</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6251,6 +6526,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670181</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6352,6 +6632,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670485</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6453,6 +6738,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670838</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6554,6 +6844,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670874</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6655,6 +6950,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670476</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6756,6 +7056,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670702</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6857,6 +7162,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670722</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6958,6 +7268,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670981</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7064,6 +7379,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670513</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7170,6 +7490,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670541</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7276,6 +7601,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670556</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7381,6 +7711,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670574</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7491,6 +7826,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407060</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7601,6 +7941,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407083</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7711,6 +8056,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407098</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7821,6 +8171,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407111</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7931,6 +8286,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407127</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8041,6 +8401,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407137</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8150,6 +8515,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669856</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8255,6 +8625,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670094</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8360,6 +8735,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405777</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8465,6 +8845,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407156</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8570,6 +8955,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407169</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8675,6 +9065,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407185</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8780,6 +9175,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407195</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8885,6 +9285,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407205</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8990,6 +9395,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407225</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9095,6 +9505,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407236</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9215,6 +9630,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448394</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9335,6 +9755,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448816</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9455,6 +9880,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448842</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9575,6 +10005,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448854</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9695,6 +10130,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448981</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9815,6 +10255,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448995</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9922,6 +10367,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671018</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10028,6 +10478,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671090</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10129,6 +10584,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669907</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10230,6 +10690,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669984</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10331,6 +10796,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670118</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10432,6 +10902,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670309</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10533,6 +11008,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670319</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10634,6 +11114,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670445</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10735,6 +11220,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670448</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10836,6 +11326,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670496</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10937,6 +11432,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670710</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11038,6 +11538,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670731</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11139,8 +11644,116 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671129</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406923</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135406928</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135406980</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135407060</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>135407083</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>135407098</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>135407111</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>135407127</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>135407137</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135405777</v>
       </c>
       <c r="B76" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135407156</v>
       </c>
       <c r="B77" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135407169</v>
       </c>
       <c r="B78" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>135407185</v>
       </c>
       <c r="B79" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135407195</v>
       </c>
       <c r="B80" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>135407205</v>
       </c>
       <c r="B81" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135407225</v>
       </c>
       <c r="B82" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>135407236</v>
       </c>
       <c r="B83" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135448394</v>
       </c>
       <c r="B84" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>135448816</v>
       </c>
       <c r="B85" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>135448842</v>
       </c>
       <c r="B86" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>135448854</v>
       </c>
       <c r="B87" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135448981</v>
       </c>
       <c r="B88" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>135448995</v>
       </c>
       <c r="B89" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1661,7 +1661,7 @@
         <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,37 +680,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127671194</v>
+        <v>135406923</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>57167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449456</v>
+        <v>449069</v>
       </c>
       <c r="R2" t="n">
-        <v>6720223</v>
+        <v>6720040</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,43 +784,48 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671194</t>
+          <t>https://artportalen.se/Sighting/135406923</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127671229</v>
+        <v>135406928</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449442</v>
+        <v>449081</v>
       </c>
       <c r="R3" t="n">
-        <v>6720178</v>
+        <v>6720036</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -854,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,47 +894,48 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671229</t>
+          <t>https://artportalen.se/Sighting/135406928</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127670266</v>
+        <v>135406980</v>
       </c>
       <c r="B4" t="n">
-        <v>93197</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449176</v>
+        <v>449081</v>
       </c>
       <c r="R4" t="n">
-        <v>6720025</v>
+        <v>6720030</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -964,12 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,16 +1004,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670266</t>
+          <t>https://artportalen.se/Sighting/135406980</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127670054</v>
+        <v>127671194</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,28 +1021,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1044,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449185</v>
+        <v>449456</v>
       </c>
       <c r="R5" t="n">
-        <v>6720192</v>
+        <v>6720223</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1106,16 +1110,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670054</t>
+          <t>https://artportalen.se/Sighting/127671194</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127670335</v>
+        <v>127671229</v>
       </c>
       <c r="B6" t="n">
-        <v>91930</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449221</v>
+        <v>449442</v>
       </c>
       <c r="R6" t="n">
-        <v>6720036</v>
+        <v>6720178</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1212,16 +1216,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670335</t>
+          <t>https://artportalen.se/Sighting/127671229</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127670907</v>
+        <v>127670266</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,26 +1233,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1260,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449605</v>
+        <v>449176</v>
       </c>
       <c r="R7" t="n">
-        <v>6720348</v>
+        <v>6720025</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1322,41 +1326,45 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670907</t>
+          <t>https://artportalen.se/Sighting/127670266</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127670000</v>
+        <v>127670054</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1366,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449159</v>
+        <v>449185</v>
       </c>
       <c r="R8" t="n">
-        <v>6720222</v>
+        <v>6720192</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1428,38 +1436,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670000</t>
+          <t>https://artportalen.se/Sighting/127670054</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127670008</v>
+        <v>127670335</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449167</v>
+        <v>449221</v>
       </c>
       <c r="R9" t="n">
-        <v>6720240</v>
+        <v>6720036</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1534,41 +1542,45 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670008</t>
+          <t>https://artportalen.se/Sighting/127670335</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127670032</v>
+        <v>127670907</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1578,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449165</v>
+        <v>449605</v>
       </c>
       <c r="R10" t="n">
-        <v>6720228</v>
+        <v>6720348</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1640,38 +1652,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670032</t>
+          <t>https://artportalen.se/Sighting/127670907</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127670132</v>
+        <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449194</v>
+        <v>449228</v>
       </c>
       <c r="R11" t="n">
-        <v>6720159</v>
+        <v>6720113</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1714,12 +1726,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,38 +1758,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670132</t>
+          <t>https://artportalen.se/Sighting/135407008</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127670152</v>
+        <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449210</v>
+        <v>449244</v>
       </c>
       <c r="R12" t="n">
-        <v>6720149</v>
+        <v>6720123</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1820,12 +1832,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,13 +1864,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670152</t>
+          <t>https://artportalen.se/Sighting/135407036</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127670168</v>
+        <v>127670000</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1896,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449195</v>
+        <v>449159</v>
       </c>
       <c r="R13" t="n">
-        <v>6720146</v>
+        <v>6720222</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1958,13 +1970,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670168</t>
+          <t>https://artportalen.se/Sighting/127670000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127670200</v>
+        <v>127670008</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -2002,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449202</v>
+        <v>449167</v>
       </c>
       <c r="R14" t="n">
-        <v>6720096</v>
+        <v>6720240</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2064,13 +2076,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670200</t>
+          <t>https://artportalen.se/Sighting/127670008</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127670217</v>
+        <v>127670032</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2108,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449200</v>
+        <v>449165</v>
       </c>
       <c r="R15" t="n">
-        <v>6720125</v>
+        <v>6720228</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2170,13 +2182,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670217</t>
+          <t>https://artportalen.se/Sighting/127670032</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127670272</v>
+        <v>127670132</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2214,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449168</v>
+        <v>449194</v>
       </c>
       <c r="R16" t="n">
-        <v>6720012</v>
+        <v>6720159</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2276,13 +2288,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670272</t>
+          <t>https://artportalen.se/Sighting/127670132</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127670280</v>
+        <v>127670152</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2320,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449176</v>
+        <v>449210</v>
       </c>
       <c r="R17" t="n">
-        <v>6720013</v>
+        <v>6720149</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2382,13 +2394,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670280</t>
+          <t>https://artportalen.se/Sighting/127670152</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127670299</v>
+        <v>127670168</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2426,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449181</v>
+        <v>449195</v>
       </c>
       <c r="R18" t="n">
-        <v>6720023</v>
+        <v>6720146</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2488,13 +2500,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670299</t>
+          <t>https://artportalen.se/Sighting/127670168</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127670324</v>
+        <v>127670200</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2532,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449217</v>
+        <v>449202</v>
       </c>
       <c r="R19" t="n">
-        <v>6720024</v>
+        <v>6720096</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2594,13 +2606,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670324</t>
+          <t>https://artportalen.se/Sighting/127670200</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127670341</v>
+        <v>127670217</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2638,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449227</v>
+        <v>449200</v>
       </c>
       <c r="R20" t="n">
-        <v>6720046</v>
+        <v>6720125</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2700,13 +2712,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670341</t>
+          <t>https://artportalen.se/Sighting/127670217</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127670364</v>
+        <v>127670272</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2744,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449245</v>
+        <v>449168</v>
       </c>
       <c r="R21" t="n">
-        <v>6720058</v>
+        <v>6720012</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2806,13 +2818,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670364</t>
+          <t>https://artportalen.se/Sighting/127670272</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127670593</v>
+        <v>127670280</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2850,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449457</v>
+        <v>449176</v>
       </c>
       <c r="R22" t="n">
-        <v>6720089</v>
+        <v>6720013</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2912,13 +2924,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670593</t>
+          <t>https://artportalen.se/Sighting/127670280</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127670605</v>
+        <v>127670299</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2956,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449451</v>
+        <v>449181</v>
       </c>
       <c r="R23" t="n">
-        <v>6720105</v>
+        <v>6720023</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3018,13 +3030,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670605</t>
+          <t>https://artportalen.se/Sighting/127670299</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127670618</v>
+        <v>127670324</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3062,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449457</v>
+        <v>449217</v>
       </c>
       <c r="R24" t="n">
-        <v>6720117</v>
+        <v>6720024</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3124,13 +3136,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670618</t>
+          <t>https://artportalen.se/Sighting/127670324</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127670625</v>
+        <v>127670341</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3168,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449440</v>
+        <v>449227</v>
       </c>
       <c r="R25" t="n">
-        <v>6720118</v>
+        <v>6720046</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3230,13 +3242,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670625</t>
+          <t>https://artportalen.se/Sighting/127670341</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127670649</v>
+        <v>127670364</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3274,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449438</v>
+        <v>449245</v>
       </c>
       <c r="R26" t="n">
-        <v>6720136</v>
+        <v>6720058</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3336,13 +3348,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670649</t>
+          <t>https://artportalen.se/Sighting/127670364</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127670743</v>
+        <v>127670593</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3380,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449576</v>
+        <v>449457</v>
       </c>
       <c r="R27" t="n">
-        <v>6720141</v>
+        <v>6720089</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3442,13 +3454,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670743</t>
+          <t>https://artportalen.se/Sighting/127670593</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127670754</v>
+        <v>127670605</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3486,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449589</v>
+        <v>449451</v>
       </c>
       <c r="R28" t="n">
-        <v>6720140</v>
+        <v>6720105</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3548,13 +3560,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670754</t>
+          <t>https://artportalen.se/Sighting/127670605</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127670762</v>
+        <v>127670618</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3592,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449570</v>
+        <v>449457</v>
       </c>
       <c r="R29" t="n">
-        <v>6720155</v>
+        <v>6720117</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3654,13 +3666,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670762</t>
+          <t>https://artportalen.se/Sighting/127670618</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127670771</v>
+        <v>127670625</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3698,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449600</v>
+        <v>449440</v>
       </c>
       <c r="R30" t="n">
-        <v>6720158</v>
+        <v>6720118</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3760,13 +3772,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670771</t>
+          <t>https://artportalen.se/Sighting/127670625</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127670781</v>
+        <v>127670649</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3804,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449586</v>
+        <v>449438</v>
       </c>
       <c r="R31" t="n">
-        <v>6720154</v>
+        <v>6720136</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3866,13 +3878,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670781</t>
+          <t>https://artportalen.se/Sighting/127670649</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127670788</v>
+        <v>127670743</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3910,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449583</v>
+        <v>449576</v>
       </c>
       <c r="R32" t="n">
-        <v>6720169</v>
+        <v>6720141</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -3972,13 +3984,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670788</t>
+          <t>https://artportalen.se/Sighting/127670743</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127670825</v>
+        <v>127670754</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4016,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449573</v>
+        <v>449589</v>
       </c>
       <c r="R33" t="n">
-        <v>6720260</v>
+        <v>6720140</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4078,13 +4090,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670825</t>
+          <t>https://artportalen.se/Sighting/127670754</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127670849</v>
+        <v>127670762</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4122,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449556</v>
+        <v>449570</v>
       </c>
       <c r="R34" t="n">
-        <v>6720283</v>
+        <v>6720155</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4184,13 +4196,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670849</t>
+          <t>https://artportalen.se/Sighting/127670762</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127670889</v>
+        <v>127670771</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4228,10 +4240,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449605</v>
+        <v>449600</v>
       </c>
       <c r="R35" t="n">
-        <v>6720315</v>
+        <v>6720158</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4290,13 +4302,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670889</t>
+          <t>https://artportalen.se/Sighting/127670771</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127670921</v>
+        <v>127670781</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4334,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449580</v>
+        <v>449586</v>
       </c>
       <c r="R36" t="n">
-        <v>6720362</v>
+        <v>6720154</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4396,13 +4408,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670921</t>
+          <t>https://artportalen.se/Sighting/127670781</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127670934</v>
+        <v>127670788</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4440,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449622</v>
+        <v>449583</v>
       </c>
       <c r="R37" t="n">
-        <v>6720346</v>
+        <v>6720169</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4502,13 +4514,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670934</t>
+          <t>https://artportalen.se/Sighting/127670788</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127670953</v>
+        <v>127670825</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4546,10 +4558,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449638</v>
+        <v>449573</v>
       </c>
       <c r="R38" t="n">
-        <v>6720356</v>
+        <v>6720260</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4608,13 +4620,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670953</t>
+          <t>https://artportalen.se/Sighting/127670825</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671028</v>
+        <v>127670849</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4652,10 +4664,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449628</v>
+        <v>449556</v>
       </c>
       <c r="R39" t="n">
-        <v>6720374</v>
+        <v>6720283</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4714,13 +4726,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671028</t>
+          <t>https://artportalen.se/Sighting/127670849</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671038</v>
+        <v>127670889</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4758,10 +4770,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449628</v>
+        <v>449605</v>
       </c>
       <c r="R40" t="n">
-        <v>6720382</v>
+        <v>6720315</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4820,13 +4832,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671038</t>
+          <t>https://artportalen.se/Sighting/127670889</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671143</v>
+        <v>127670921</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -4864,10 +4876,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449435</v>
+        <v>449580</v>
       </c>
       <c r="R41" t="n">
-        <v>6720323</v>
+        <v>6720362</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -4926,13 +4938,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671143</t>
+          <t>https://artportalen.se/Sighting/127670921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127671155</v>
+        <v>127670934</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -4970,10 +4982,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449421</v>
+        <v>449622</v>
       </c>
       <c r="R42" t="n">
-        <v>6720319</v>
+        <v>6720346</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5032,13 +5044,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671155</t>
+          <t>https://artportalen.se/Sighting/127670934</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671164</v>
+        <v>127670953</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5076,10 +5088,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449428</v>
+        <v>449638</v>
       </c>
       <c r="R43" t="n">
-        <v>6720312</v>
+        <v>6720356</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5138,13 +5150,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671164</t>
+          <t>https://artportalen.se/Sighting/127670953</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671175</v>
+        <v>127671028</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5182,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449421</v>
+        <v>449628</v>
       </c>
       <c r="R44" t="n">
-        <v>6720306</v>
+        <v>6720374</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5244,13 +5256,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671175</t>
+          <t>https://artportalen.se/Sighting/127671028</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671204</v>
+        <v>127671038</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5288,10 +5300,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449443</v>
+        <v>449628</v>
       </c>
       <c r="R45" t="n">
-        <v>6720234</v>
+        <v>6720382</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5350,13 +5362,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671204</t>
+          <t>https://artportalen.se/Sighting/127671038</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671216</v>
+        <v>127671143</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5394,10 +5406,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449453</v>
+        <v>449435</v>
       </c>
       <c r="R46" t="n">
-        <v>6720203</v>
+        <v>6720323</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5456,13 +5468,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671216</t>
+          <t>https://artportalen.se/Sighting/127671143</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671236</v>
+        <v>127671155</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5500,10 +5512,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>449454</v>
+        <v>449421</v>
       </c>
       <c r="R47" t="n">
-        <v>6720176</v>
+        <v>6720319</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5562,13 +5574,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671236</t>
+          <t>https://artportalen.se/Sighting/127671155</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671241</v>
+        <v>127671164</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5606,10 +5618,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449445</v>
+        <v>449428</v>
       </c>
       <c r="R48" t="n">
-        <v>6720188</v>
+        <v>6720312</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5668,13 +5680,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671241</t>
+          <t>https://artportalen.se/Sighting/127671164</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671250</v>
+        <v>127671175</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5712,10 +5724,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449429</v>
+        <v>449421</v>
       </c>
       <c r="R49" t="n">
-        <v>6720186</v>
+        <v>6720306</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5774,13 +5786,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671250</t>
+          <t>https://artportalen.se/Sighting/127671175</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671259</v>
+        <v>127671204</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5818,10 +5830,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449417</v>
+        <v>449443</v>
       </c>
       <c r="R50" t="n">
-        <v>6720181</v>
+        <v>6720234</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5880,38 +5892,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671259</t>
+          <t>https://artportalen.se/Sighting/127671204</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127670181</v>
+        <v>127671216</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5924,10 +5936,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>449202</v>
+        <v>449453</v>
       </c>
       <c r="R51" t="n">
-        <v>6720148</v>
+        <v>6720203</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -5986,38 +5998,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670181</t>
+          <t>https://artportalen.se/Sighting/127671216</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127670485</v>
+        <v>127671236</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6042,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449358</v>
+        <v>449454</v>
       </c>
       <c r="R52" t="n">
-        <v>6720139</v>
+        <v>6720176</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6092,38 +6104,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670485</t>
+          <t>https://artportalen.se/Sighting/127671236</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127670838</v>
+        <v>127671241</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6136,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449579</v>
+        <v>449445</v>
       </c>
       <c r="R53" t="n">
-        <v>6720260</v>
+        <v>6720188</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6198,38 +6210,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670838</t>
+          <t>https://artportalen.se/Sighting/127671241</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127670874</v>
+        <v>127671250</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6242,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>449564</v>
+        <v>449429</v>
       </c>
       <c r="R54" t="n">
-        <v>6720313</v>
+        <v>6720186</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6304,38 +6316,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670874</t>
+          <t>https://artportalen.se/Sighting/127671250</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127670476</v>
+        <v>127671259</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6348,10 +6360,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>449363</v>
+        <v>449417</v>
       </c>
       <c r="R55" t="n">
-        <v>6720137</v>
+        <v>6720181</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6410,16 +6422,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670476</t>
+          <t>https://artportalen.se/Sighting/127671259</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127670702</v>
+        <v>127670181</v>
       </c>
       <c r="B56" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6427,21 +6439,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,10 +6466,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>449550</v>
+        <v>449202</v>
       </c>
       <c r="R56" t="n">
-        <v>6720131</v>
+        <v>6720148</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6516,16 +6528,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670702</t>
+          <t>https://artportalen.se/Sighting/127670181</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127670722</v>
+        <v>127670485</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6533,21 +6545,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6560,10 +6572,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>449567</v>
+        <v>449358</v>
       </c>
       <c r="R57" t="n">
-        <v>6720141</v>
+        <v>6720139</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6622,16 +6634,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670722</t>
+          <t>https://artportalen.se/Sighting/127670485</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127670981</v>
+        <v>127670838</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6639,21 +6651,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6666,10 +6678,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>449656</v>
+        <v>449579</v>
       </c>
       <c r="R58" t="n">
-        <v>6720358</v>
+        <v>6720260</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6728,16 +6740,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670981</t>
+          <t>https://artportalen.se/Sighting/127670838</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127670513</v>
+        <v>127670874</v>
       </c>
       <c r="B59" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6745,21 +6757,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6772,10 +6784,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>449366</v>
+        <v>449564</v>
       </c>
       <c r="R59" t="n">
-        <v>6720133</v>
+        <v>6720313</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6810,11 +6822,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6839,16 +6846,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670513</t>
+          <t>https://artportalen.se/Sighting/127670874</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127670541</v>
+        <v>127670476</v>
       </c>
       <c r="B60" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6856,21 +6863,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6883,10 +6890,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>449410</v>
+        <v>449363</v>
       </c>
       <c r="R60" t="n">
-        <v>6720148</v>
+        <v>6720137</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -6921,11 +6928,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6950,16 +6952,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670541</t>
+          <t>https://artportalen.se/Sighting/127670476</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127670556</v>
+        <v>127670702</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6967,21 +6969,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6994,10 +6996,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>449417</v>
+        <v>449550</v>
       </c>
       <c r="R61" t="n">
-        <v>6720161</v>
+        <v>6720131</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7032,11 +7034,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Mycket riklig förekomst på gammal grov asp.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7061,48 +7058,43 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670556</t>
+          <t>https://artportalen.se/Sighting/127670702</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127670574</v>
+        <v>127670722</v>
       </c>
       <c r="B62" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7110,10 +7102,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>449419</v>
+        <v>449567</v>
       </c>
       <c r="R62" t="n">
-        <v>6720156</v>
+        <v>6720141</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7154,6 +7146,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7171,52 +7164,43 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670574</t>
+          <t>https://artportalen.se/Sighting/127670722</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127669856</v>
+        <v>127670981</v>
       </c>
       <c r="B63" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7224,10 +7208,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>449125</v>
+        <v>449656</v>
       </c>
       <c r="R63" t="n">
-        <v>6720233</v>
+        <v>6720358</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7268,6 +7252,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7285,48 +7270,43 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127669856</t>
+          <t>https://artportalen.se/Sighting/127670981</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127670094</v>
+        <v>127670513</v>
       </c>
       <c r="B64" t="n">
-        <v>57141</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7334,10 +7314,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>449196</v>
+        <v>449366</v>
       </c>
       <c r="R64" t="n">
-        <v>6720173</v>
+        <v>6720133</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7372,12 +7352,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7395,49 +7381,43 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670094</t>
+          <t>https://artportalen.se/Sighting/127670513</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671018</v>
+        <v>127670541</v>
       </c>
       <c r="B65" t="n">
-        <v>8455</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7445,10 +7425,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>449633</v>
+        <v>449410</v>
       </c>
       <c r="R65" t="n">
-        <v>6720378</v>
+        <v>6720148</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7483,6 +7463,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7507,48 +7492,43 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671018</t>
+          <t>https://artportalen.se/Sighting/127670541</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127671090</v>
+        <v>127670556</v>
       </c>
       <c r="B66" t="n">
-        <v>99038</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7556,10 +7536,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>449480</v>
+        <v>449417</v>
       </c>
       <c r="R66" t="n">
-        <v>6720296</v>
+        <v>6720161</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7594,6 +7574,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket riklig förekomst på gammal grov asp.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7618,43 +7603,48 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127671090</t>
+          <t>https://artportalen.se/Sighting/127670556</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127669907</v>
+        <v>127670574</v>
       </c>
       <c r="B67" t="n">
-        <v>79085</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7662,10 +7652,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>449153</v>
+        <v>449419</v>
       </c>
       <c r="R67" t="n">
-        <v>6720237</v>
+        <v>6720156</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7706,7 +7696,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7724,16 +7713,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127669907</t>
+          <t>https://artportalen.se/Sighting/127670574</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127669984</v>
+        <v>135407060</v>
       </c>
       <c r="B68" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,26 +7730,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7768,10 +7762,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>449175</v>
+        <v>449236</v>
       </c>
       <c r="R68" t="n">
-        <v>6720229</v>
+        <v>6720036</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7798,12 +7792,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7812,7 +7811,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7830,16 +7828,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127669984</t>
+          <t>https://artportalen.se/Sighting/135407060</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127670118</v>
+        <v>135407083</v>
       </c>
       <c r="B69" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7847,26 +7845,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7874,10 +7877,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>449175</v>
+        <v>449247</v>
       </c>
       <c r="R69" t="n">
-        <v>6720175</v>
+        <v>6720048</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -7904,12 +7907,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7918,7 +7926,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7936,16 +7943,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670118</t>
+          <t>https://artportalen.se/Sighting/135407083</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127670309</v>
+        <v>135407098</v>
       </c>
       <c r="B70" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7953,26 +7960,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7980,10 +7992,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>449202</v>
+        <v>449230</v>
       </c>
       <c r="R70" t="n">
-        <v>6720026</v>
+        <v>6720102</v>
       </c>
       <c r="S70" t="n">
         <v>50</v>
@@ -8010,12 +8022,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8024,7 +8041,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8042,16 +8058,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670309</t>
+          <t>https://artportalen.se/Sighting/135407098</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127670319</v>
+        <v>135407111</v>
       </c>
       <c r="B71" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8059,26 +8075,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8086,10 +8107,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>449199</v>
+        <v>449176</v>
       </c>
       <c r="R71" t="n">
-        <v>6720015</v>
+        <v>6720201</v>
       </c>
       <c r="S71" t="n">
         <v>50</v>
@@ -8116,12 +8137,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8130,7 +8156,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8148,16 +8173,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670319</t>
+          <t>https://artportalen.se/Sighting/135407111</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127670445</v>
+        <v>135407127</v>
       </c>
       <c r="B72" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8165,26 +8190,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8192,10 +8222,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>449296</v>
+        <v>449187</v>
       </c>
       <c r="R72" t="n">
-        <v>6720275</v>
+        <v>6720212</v>
       </c>
       <c r="S72" t="n">
         <v>50</v>
@@ -8222,12 +8252,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8236,7 +8271,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8254,16 +8288,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670445</t>
+          <t>https://artportalen.se/Sighting/135407127</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127670448</v>
+        <v>135407137</v>
       </c>
       <c r="B73" t="n">
-        <v>79085</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8271,26 +8305,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8298,10 +8337,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>449292</v>
+        <v>449192</v>
       </c>
       <c r="R73" t="n">
-        <v>6720271</v>
+        <v>6720196</v>
       </c>
       <c r="S73" t="n">
         <v>50</v>
@@ -8328,12 +8367,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8342,7 +8386,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8360,43 +8403,52 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670448</t>
+          <t>https://artportalen.se/Sighting/135407137</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127670496</v>
+        <v>127669856</v>
       </c>
       <c r="B74" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8404,10 +8456,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>449359</v>
+        <v>449125</v>
       </c>
       <c r="R74" t="n">
-        <v>6720133</v>
+        <v>6720233</v>
       </c>
       <c r="S74" t="n">
         <v>50</v>
@@ -8448,7 +8500,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8466,43 +8517,48 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670496</t>
+          <t>https://artportalen.se/Sighting/127669856</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127670710</v>
+        <v>127670094</v>
       </c>
       <c r="B75" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8510,10 +8566,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>449560</v>
+        <v>449196</v>
       </c>
       <c r="R75" t="n">
-        <v>6720133</v>
+        <v>6720173</v>
       </c>
       <c r="S75" t="n">
         <v>50</v>
@@ -8554,7 +8610,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8572,43 +8627,48 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670710</t>
+          <t>https://artportalen.se/Sighting/127670094</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127670731</v>
+        <v>135405777</v>
       </c>
       <c r="B76" t="n">
-        <v>79085</v>
+        <v>57167</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8616,10 +8676,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>449569</v>
+        <v>449287</v>
       </c>
       <c r="R76" t="n">
-        <v>6720138</v>
+        <v>6720229</v>
       </c>
       <c r="S76" t="n">
         <v>50</v>
@@ -8646,12 +8706,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8660,7 +8720,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8678,43 +8737,48 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127670731</t>
+          <t>https://artportalen.se/Sighting/135405777</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127671129</v>
+        <v>135407156</v>
       </c>
       <c r="B77" t="n">
-        <v>79085</v>
+        <v>57167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8722,10 +8786,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>449427</v>
+        <v>449198</v>
       </c>
       <c r="R77" t="n">
-        <v>6720322</v>
+        <v>6720054</v>
       </c>
       <c r="S77" t="n">
         <v>50</v>
@@ -8752,12 +8816,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8766,7 +8830,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8783,6 +8846,2805 @@
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407156</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135407169</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>449231</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6720053</v>
+      </c>
+      <c r="S78" t="n">
+        <v>50</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407169</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135407185</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>449169</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6720150</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407185</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135407195</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>449157</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6720238</v>
+      </c>
+      <c r="S80" t="n">
+        <v>50</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407195</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135407205</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>449174</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6720215</v>
+      </c>
+      <c r="S81" t="n">
+        <v>50</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407205</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135407225</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>449185</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6720200</v>
+      </c>
+      <c r="S82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407225</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135407236</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>449494</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S83" t="n">
+        <v>50</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135407236</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135448394</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>449299</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6720032</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färsk spillning på sten</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448394</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135448816</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>449149</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6720071</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Tjäderspillning på låg sten</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448816</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135448842</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>449177</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6720087</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>på sten</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448842</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135448854</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>449141</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6720065</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Sandbad</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448854</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135448981</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>449090</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6720042</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>på sten</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448981</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135448995</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>449098</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6720041</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>på sten</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135448995</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127671018</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>449633</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6720378</v>
+      </c>
+      <c r="S90" t="n">
+        <v>50</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671018</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127671090</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>449480</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6720296</v>
+      </c>
+      <c r="S91" t="n">
+        <v>50</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671090</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127669907</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>449153</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6720237</v>
+      </c>
+      <c r="S92" t="n">
+        <v>50</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669907</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127669984</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>449175</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6720229</v>
+      </c>
+      <c r="S93" t="n">
+        <v>50</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127669984</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127670118</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>449175</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6720175</v>
+      </c>
+      <c r="S94" t="n">
+        <v>50</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670118</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127670309</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>449202</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6720026</v>
+      </c>
+      <c r="S95" t="n">
+        <v>50</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670309</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127670319</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>449199</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6720015</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670319</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127670445</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>449296</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6720275</v>
+      </c>
+      <c r="S97" t="n">
+        <v>50</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670445</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127670448</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>449292</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6720271</v>
+      </c>
+      <c r="S98" t="n">
+        <v>50</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670448</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127670496</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>449359</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S99" t="n">
+        <v>50</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670496</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127670710</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>449560</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6720133</v>
+      </c>
+      <c r="S100" t="n">
+        <v>50</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670710</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127670731</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>449569</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6720138</v>
+      </c>
+      <c r="S101" t="n">
+        <v>50</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127670731</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127671129</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bergmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>449427</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6720322</v>
+      </c>
+      <c r="S102" t="n">
+        <v>50</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127671129</t>
         </is>
@@ -8866,6 +11728,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -1661,7 +1661,7 @@
         <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37715-2025 artfynd.xlsx
+++ b/artfynd/A 37715-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406923</v>
       </c>
       <c r="B2" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135406928</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135406980</v>
       </c>
       <c r="B4" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>135407008</v>
       </c>
       <c r="B11" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135407036</v>
       </c>
       <c r="B12" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135407060</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>135407083</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>135407098</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>135407111</v>
       </c>
       <c r="B71" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>135407127</v>
       </c>
       <c r="B72" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>135407137</v>
       </c>
       <c r="B73" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>135405777</v>
       </c>
       <c r="B76" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>135407156</v>
       </c>
       <c r="B77" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135407169</v>
       </c>
       <c r="B78" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>135407185</v>
       </c>
       <c r="B79" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>135407195</v>
       </c>
       <c r="B80" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>135407205</v>
       </c>
       <c r="B81" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135407225</v>
       </c>
       <c r="B82" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>135407236</v>
       </c>
       <c r="B83" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>135448394</v>
       </c>
       <c r="B84" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>135448816</v>
       </c>
       <c r="B85" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>135448842</v>
       </c>
       <c r="B86" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>135448854</v>
       </c>
       <c r="B87" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135448981</v>
       </c>
       <c r="B88" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>135448995</v>
       </c>
       <c r="B89" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
